--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92B276C-7741-4B04-979E-0E5BB7963E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5CFB02-FC76-4BFD-BD25-BB74C8F1C69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="100">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -329,6 +329,56 @@
   </si>
   <si>
     <t>攻击_招架支援_H_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.ActionResilience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resilience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韧性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提尔锋感染</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,0</t>
+  </si>
+  <si>
+    <t>5,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -693,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
@@ -702,7 +752,7 @@
     <col min="7" max="7" width="42.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -724,8 +774,11 @@
       <c r="G1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -744,13 +797,16 @@
       <c r="G2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -772,8 +828,11 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -783,8 +842,11 @@
       <c r="D5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -794,8 +856,11 @@
       <c r="D6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -805,8 +870,11 @@
       <c r="D7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>13</v>
       </c>
@@ -816,8 +884,11 @@
       <c r="D8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>13</v>
       </c>
@@ -827,8 +898,11 @@
       <c r="D9" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>13</v>
       </c>
@@ -838,8 +912,11 @@
       <c r="D10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>13</v>
       </c>
@@ -849,8 +926,11 @@
       <c r="D11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>13</v>
       </c>
@@ -860,8 +940,11 @@
       <c r="D12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>13</v>
       </c>
@@ -871,8 +954,11 @@
       <c r="D13" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>13</v>
       </c>
@@ -882,8 +968,11 @@
       <c r="D14" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>13</v>
       </c>
@@ -893,8 +982,11 @@
       <c r="D15" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>13</v>
       </c>
@@ -904,8 +996,11 @@
       <c r="D16" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>13</v>
       </c>
@@ -915,8 +1010,11 @@
       <c r="D17" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>13</v>
       </c>
@@ -926,8 +1024,11 @@
       <c r="D18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>13</v>
       </c>
@@ -937,8 +1038,11 @@
       <c r="D19" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>13</v>
       </c>
@@ -948,8 +1052,11 @@
       <c r="D20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>13</v>
       </c>
@@ -959,8 +1066,11 @@
       <c r="D21" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>13</v>
       </c>
@@ -970,8 +1080,11 @@
       <c r="D22" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>13</v>
       </c>
@@ -981,8 +1094,11 @@
       <c r="D23" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>13</v>
       </c>
@@ -992,8 +1108,11 @@
       <c r="D24" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>13</v>
       </c>
@@ -1003,8 +1122,11 @@
       <c r="D25" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>13</v>
       </c>
@@ -1014,8 +1136,11 @@
       <c r="D26" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>13</v>
       </c>
@@ -1025,8 +1150,11 @@
       <c r="D27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>13</v>
       </c>
@@ -1036,8 +1164,11 @@
       <c r="D28" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>14</v>
       </c>
@@ -1047,8 +1178,11 @@
       <c r="D29" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>14</v>
       </c>
@@ -1058,8 +1192,11 @@
       <c r="D30" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>14</v>
       </c>
@@ -1069,8 +1206,11 @@
       <c r="D31" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>14</v>
       </c>
@@ -1080,8 +1220,11 @@
       <c r="D32" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>14</v>
       </c>
@@ -1091,8 +1234,11 @@
       <c r="D33" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>14</v>
       </c>
@@ -1102,8 +1248,11 @@
       <c r="D34" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>14</v>
       </c>
@@ -1113,8 +1262,11 @@
       <c r="D35" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>14</v>
       </c>
@@ -1124,8 +1276,11 @@
       <c r="D36" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>14</v>
       </c>
@@ -1135,8 +1290,11 @@
       <c r="D37" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1304,11 @@
       <c r="D38" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>14</v>
       </c>
@@ -1157,8 +1318,11 @@
       <c r="D39" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>14</v>
       </c>
@@ -1168,8 +1332,11 @@
       <c r="D40" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>14</v>
       </c>
@@ -1179,8 +1346,11 @@
       <c r="D41" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>14</v>
       </c>
@@ -1190,8 +1360,11 @@
       <c r="D42" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>14</v>
       </c>
@@ -1201,8 +1374,11 @@
       <c r="D43" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>14</v>
       </c>
@@ -1212,8 +1388,11 @@
       <c r="D44" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>14</v>
       </c>
@@ -1223,8 +1402,11 @@
       <c r="D45" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>14</v>
       </c>
@@ -1234,8 +1416,11 @@
       <c r="D46" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>14</v>
       </c>
@@ -1245,8 +1430,11 @@
       <c r="D47" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>14</v>
       </c>
@@ -1256,8 +1444,11 @@
       <c r="D48" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>14</v>
       </c>
@@ -1267,8 +1458,11 @@
       <c r="D49" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>79</v>
       </c>
@@ -1278,8 +1472,11 @@
       <c r="D50" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>79</v>
       </c>
@@ -1289,8 +1486,11 @@
       <c r="D51" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>79</v>
       </c>
@@ -1300,8 +1500,11 @@
       <c r="D52" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>79</v>
       </c>
@@ -1311,8 +1514,11 @@
       <c r="D53" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>79</v>
       </c>
@@ -1322,8 +1528,11 @@
       <c r="D54" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>79</v>
       </c>
@@ -1333,8 +1542,11 @@
       <c r="D55" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>79</v>
       </c>
@@ -1344,8 +1556,11 @@
       <c r="D56" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>79</v>
       </c>
@@ -1355,8 +1570,11 @@
       <c r="D57" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>79</v>
       </c>
@@ -1366,8 +1584,11 @@
       <c r="D58" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>79</v>
       </c>
@@ -1377,8 +1598,11 @@
       <c r="D59" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>79</v>
       </c>
@@ -1388,8 +1612,11 @@
       <c r="D60" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>79</v>
       </c>
@@ -1399,8 +1626,11 @@
       <c r="D61" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>79</v>
       </c>
@@ -1410,8 +1640,11 @@
       <c r="D62" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
         <v>79</v>
       </c>
@@ -1421,8 +1654,11 @@
       <c r="D63" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>79</v>
       </c>
@@ -1432,8 +1668,11 @@
       <c r="D64" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>79</v>
       </c>
@@ -1443,8 +1682,11 @@
       <c r="D65" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>79</v>
       </c>
@@ -1454,8 +1696,11 @@
       <c r="D66" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H66" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
         <v>79</v>
       </c>
@@ -1465,8 +1710,11 @@
       <c r="D67" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
         <v>79</v>
       </c>
@@ -1476,8 +1724,11 @@
       <c r="D68" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
         <v>79</v>
       </c>
@@ -1487,8 +1738,11 @@
       <c r="D69" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H69" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
         <v>79</v>
       </c>
@@ -1504,8 +1758,11 @@
       <c r="G70" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H70" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
         <v>79</v>
       </c>
@@ -1521,8 +1778,11 @@
       <c r="G71" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H71" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
         <v>79</v>
       </c>
@@ -1538,8 +1798,11 @@
       <c r="G72" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H72" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
         <v>79</v>
       </c>
@@ -1549,8 +1812,11 @@
       <c r="D73" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H73" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
         <v>79</v>
       </c>
@@ -1566,8 +1832,11 @@
       <c r="G74" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H74" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>79</v>
       </c>
@@ -1583,8 +1852,11 @@
       <c r="G75" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H75" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>79</v>
       </c>
@@ -1594,8 +1866,11 @@
       <c r="D76" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H76" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
         <v>79</v>
       </c>
@@ -1605,8 +1880,11 @@
       <c r="D77" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H77" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
         <v>79</v>
       </c>
@@ -1616,8 +1894,11 @@
       <c r="D78" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H78" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
         <v>79</v>
       </c>
@@ -1627,8 +1908,11 @@
       <c r="D79" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H79" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
         <v>79</v>
       </c>
@@ -1638,8 +1922,11 @@
       <c r="D80" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H80" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
         <v>79</v>
       </c>
@@ -1649,8 +1936,11 @@
       <c r="D81" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H81" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
         <v>79</v>
       </c>
@@ -1666,8 +1956,11 @@
       <c r="G82" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H82" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
         <v>79</v>
       </c>
@@ -1677,8 +1970,11 @@
       <c r="D83" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H83" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
         <v>79</v>
       </c>
@@ -1688,8 +1984,11 @@
       <c r="D84" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H84" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
         <v>79</v>
       </c>
@@ -1699,8 +1998,11 @@
       <c r="D85" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="H85" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
         <v>79</v>
       </c>
@@ -1709,6 +2011,37 @@
       </c>
       <c r="D86" t="s">
         <v>86</v>
+      </c>
+      <c r="H86" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+      <c r="C87">
+        <v>200040</v>
+      </c>
+      <c r="D87" t="s">
+        <v>91</v>
+      </c>
+      <c r="H87" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B88" t="s">
+        <v>90</v>
+      </c>
+      <c r="C88">
+        <v>200050</v>
+      </c>
+      <c r="D88" t="s">
+        <v>93</v>
+      </c>
+      <c r="H88" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E5CFB02-FC76-4BFD-BD25-BB74C8F1C69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBDCC1F-6AC2-4D15-93C6-0CB548D7172D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="107">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -324,14 +324,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_招架支援_H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_招架支援_H_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.ActionResilience</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -379,6 +371,42 @@
   </si>
   <si>
     <t>5,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架反击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_重</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_重_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_轻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_招架支援_轻_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssistPoint,GreaterEqual,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssistPoint,GreaterEqual,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssistPoint,FixedValue,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssistPoint,FixedValue,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -743,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
@@ -775,7 +803,7 @@
         <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -798,7 +826,7 @@
         <v>78</v>
       </c>
       <c r="H2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -829,7 +857,7 @@
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -843,7 +871,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -857,7 +885,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -871,7 +899,7 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -885,7 +913,7 @@
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -899,7 +927,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -913,7 +941,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -927,7 +955,7 @@
         <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -941,7 +969,7 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -955,7 +983,7 @@
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -969,7 +997,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -983,7 +1011,7 @@
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -997,7 +1025,7 @@
         <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -1011,7 +1039,7 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1025,7 +1053,7 @@
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1039,7 +1067,7 @@
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1053,7 +1081,7 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1067,7 +1095,7 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1081,7 +1109,7 @@
         <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -1095,7 +1123,7 @@
         <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -1109,7 +1137,7 @@
         <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -1123,7 +1151,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -1137,7 +1165,7 @@
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -1151,7 +1179,7 @@
         <v>37</v>
       </c>
       <c r="H27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -1165,7 +1193,7 @@
         <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -1179,7 +1207,7 @@
         <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -1193,7 +1221,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -1207,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -1221,7 +1249,7 @@
         <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -1235,7 +1263,7 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -1249,7 +1277,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -1263,7 +1291,7 @@
         <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -1277,7 +1305,7 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -1291,7 +1319,7 @@
         <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -1305,7 +1333,7 @@
         <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -1319,7 +1347,7 @@
         <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -1333,7 +1361,7 @@
         <v>43</v>
       </c>
       <c r="H40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -1347,7 +1375,7 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -1361,7 +1389,7 @@
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
@@ -1375,7 +1403,7 @@
         <v>46</v>
       </c>
       <c r="H43" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -1389,7 +1417,7 @@
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -1403,7 +1431,7 @@
         <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -1417,7 +1445,7 @@
         <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
@@ -1431,7 +1459,7 @@
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -1445,7 +1473,7 @@
         <v>37</v>
       </c>
       <c r="H48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -1459,7 +1487,7 @@
         <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
@@ -1473,7 +1501,7 @@
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
@@ -1487,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -1501,7 +1529,7 @@
         <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
@@ -1515,7 +1543,7 @@
         <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
@@ -1529,7 +1557,7 @@
         <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
@@ -1543,7 +1571,7 @@
         <v>51</v>
       </c>
       <c r="H55" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
@@ -1557,7 +1585,7 @@
         <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
@@ -1571,7 +1599,7 @@
         <v>39</v>
       </c>
       <c r="H57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
@@ -1585,7 +1613,7 @@
         <v>53</v>
       </c>
       <c r="H58" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
@@ -1599,7 +1627,7 @@
         <v>54</v>
       </c>
       <c r="H59" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
@@ -1613,7 +1641,7 @@
         <v>47</v>
       </c>
       <c r="H60" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
@@ -1627,7 +1655,7 @@
         <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
@@ -1641,7 +1669,7 @@
         <v>37</v>
       </c>
       <c r="H62" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
@@ -1655,7 +1683,7 @@
         <v>38</v>
       </c>
       <c r="H63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
@@ -1669,7 +1697,7 @@
         <v>40</v>
       </c>
       <c r="H64" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
@@ -1683,7 +1711,7 @@
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
@@ -1697,7 +1725,7 @@
         <v>66</v>
       </c>
       <c r="H66" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
@@ -1711,7 +1739,7 @@
         <v>67</v>
       </c>
       <c r="H67" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
@@ -1725,7 +1753,7 @@
         <v>68</v>
       </c>
       <c r="H68" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
@@ -1739,7 +1767,7 @@
         <v>69</v>
       </c>
       <c r="H69" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
@@ -1759,7 +1787,7 @@
         <v>77</v>
       </c>
       <c r="H70" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
@@ -1779,7 +1807,7 @@
         <v>77</v>
       </c>
       <c r="H71" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
@@ -1799,7 +1827,7 @@
         <v>77</v>
       </c>
       <c r="H72" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
@@ -1813,7 +1841,7 @@
         <v>45</v>
       </c>
       <c r="H73" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
@@ -1833,7 +1861,7 @@
         <v>76</v>
       </c>
       <c r="H74" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.2">
@@ -1853,7 +1881,7 @@
         <v>76</v>
       </c>
       <c r="H75" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
@@ -1867,7 +1895,7 @@
         <v>49</v>
       </c>
       <c r="H76" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
@@ -1881,7 +1909,7 @@
         <v>57</v>
       </c>
       <c r="H77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.2">
@@ -1895,7 +1923,7 @@
         <v>62</v>
       </c>
       <c r="H78" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.2">
@@ -1909,7 +1937,7 @@
         <v>63</v>
       </c>
       <c r="H79" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.2">
@@ -1923,7 +1951,7 @@
         <v>64</v>
       </c>
       <c r="H80" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
@@ -1937,7 +1965,7 @@
         <v>65</v>
       </c>
       <c r="H81" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
@@ -1957,7 +1985,7 @@
         <v>83</v>
       </c>
       <c r="H82" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
@@ -1971,7 +1999,7 @@
         <v>80</v>
       </c>
       <c r="H83" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
@@ -1985,7 +2013,7 @@
         <v>84</v>
       </c>
       <c r="H84" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
@@ -1996,10 +2024,16 @@
         <v>140350</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>101</v>
+      </c>
+      <c r="F85" t="s">
+        <v>103</v>
+      </c>
+      <c r="G85" t="s">
+        <v>105</v>
       </c>
       <c r="H85" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
@@ -2010,38 +2044,86 @@
         <v>140360</v>
       </c>
       <c r="D86" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="H86" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87">
+        <v>140370</v>
+      </c>
+      <c r="D87" t="s">
+        <v>99</v>
+      </c>
+      <c r="F87" t="s">
+        <v>104</v>
+      </c>
+      <c r="G87" t="s">
+        <v>106</v>
+      </c>
+      <c r="H87" t="s">
         <v>90</v>
-      </c>
-      <c r="C87">
-        <v>200040</v>
-      </c>
-      <c r="D87" t="s">
-        <v>91</v>
-      </c>
-      <c r="H87" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88">
+        <v>140380</v>
+      </c>
+      <c r="D88" t="s">
+        <v>100</v>
+      </c>
+      <c r="H88" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B89" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89">
+        <v>140390</v>
+      </c>
+      <c r="D89" t="s">
+        <v>98</v>
+      </c>
+      <c r="H89" t="s">
         <v>90</v>
       </c>
-      <c r="C88">
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B90" t="s">
+        <v>88</v>
+      </c>
+      <c r="C90">
+        <v>200040</v>
+      </c>
+      <c r="D90" t="s">
+        <v>89</v>
+      </c>
+      <c r="H90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B91" t="s">
+        <v>88</v>
+      </c>
+      <c r="C91">
         <v>200050</v>
       </c>
-      <c r="D88" t="s">
-        <v>93</v>
-      </c>
-      <c r="H88" t="s">
-        <v>94</v>
+      <c r="D91" t="s">
+        <v>91</v>
+      </c>
+      <c r="H91" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBDCC1F-6AC2-4D15-93C6-0CB548D7172D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1236406-4F44-4556-B7B8-C10C9A5553D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="142">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -224,10 +224,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_普通攻击_3_急冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击_特殊技_3_急冻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -248,22 +244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_普通攻击_3_向前_近</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3_向前_远</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3_后撤_近</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3_后撤_远</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(list),ZZZ.AttributeCondition</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -407,6 +387,165 @@
   </si>
   <si>
     <t>AssistPoint,FixedValue,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_近</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_急冻_近</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_普通攻击_3_急冻_远</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk_Start_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk_Start2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Run_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwitchIn_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwitchOut_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Front</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Normal_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Normal_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Normal_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Normal_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Normal_06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Normal_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Branch_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Rush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Branch_02</t>
+  </si>
+  <si>
+    <t>Attack_Normal_05_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Front_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Front_LeftFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Front_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Front_RightFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Back_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Back_LeftFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Back_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Back_RightFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evade_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_ExSpecial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_ExSpecial_02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -771,7 +910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
@@ -797,13 +936,13 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -820,13 +959,13 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -851,13 +990,13 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -871,7 +1010,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -885,7 +1024,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -899,7 +1038,7 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -913,7 +1052,7 @@
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -927,7 +1066,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -941,7 +1080,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -955,7 +1094,7 @@
         <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -969,7 +1108,7 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -983,7 +1122,7 @@
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -997,7 +1136,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1011,7 +1150,7 @@
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1025,7 +1164,7 @@
         <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -1039,7 +1178,7 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1053,7 +1192,7 @@
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1067,7 +1206,7 @@
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1081,7 +1220,7 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1095,7 +1234,7 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1109,7 +1248,7 @@
         <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -1123,7 +1262,7 @@
         <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -1137,7 +1276,7 @@
         <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -1151,7 +1290,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -1165,7 +1304,7 @@
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -1179,7 +1318,7 @@
         <v>37</v>
       </c>
       <c r="H27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -1193,7 +1332,7 @@
         <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -1207,7 +1346,7 @@
         <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -1221,7 +1360,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -1235,7 +1374,7 @@
         <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -1249,7 +1388,7 @@
         <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -1263,7 +1402,7 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -1277,7 +1416,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -1291,7 +1430,7 @@
         <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -1305,7 +1444,7 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -1319,7 +1458,7 @@
         <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -1333,7 +1472,7 @@
         <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -1347,7 +1486,7 @@
         <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -1361,7 +1500,7 @@
         <v>43</v>
       </c>
       <c r="H40" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -1375,7 +1514,7 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -1389,7 +1528,7 @@
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
@@ -1403,7 +1542,7 @@
         <v>46</v>
       </c>
       <c r="H43" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -1417,7 +1556,7 @@
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -1431,7 +1570,7 @@
         <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -1445,7 +1584,7 @@
         <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
@@ -1459,7 +1598,7 @@
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -1473,7 +1612,7 @@
         <v>37</v>
       </c>
       <c r="H48" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -1487,12 +1626,12 @@
         <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C50">
         <v>140000</v>
@@ -1501,12 +1640,12 @@
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>140010</v>
@@ -1515,12 +1654,12 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>140020</v>
@@ -1529,12 +1668,12 @@
         <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>140030</v>
@@ -1543,12 +1682,12 @@
         <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <v>140040</v>
@@ -1557,12 +1696,12 @@
         <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C55">
         <v>140050</v>
@@ -1571,12 +1710,12 @@
         <v>51</v>
       </c>
       <c r="H55" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C56">
         <v>140060</v>
@@ -1585,12 +1724,12 @@
         <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C57">
         <v>140070</v>
@@ -1599,12 +1738,12 @@
         <v>39</v>
       </c>
       <c r="H57" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>140080</v>
@@ -1613,12 +1752,12 @@
         <v>53</v>
       </c>
       <c r="H58" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C59">
         <v>140090</v>
@@ -1627,12 +1766,12 @@
         <v>54</v>
       </c>
       <c r="H59" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C60">
         <v>140100</v>
@@ -1641,12 +1780,12 @@
         <v>47</v>
       </c>
       <c r="H60" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C61">
         <v>140110</v>
@@ -1655,12 +1794,12 @@
         <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C62">
         <v>140120</v>
@@ -1669,12 +1808,12 @@
         <v>37</v>
       </c>
       <c r="H62" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C63">
         <v>140130</v>
@@ -1683,12 +1822,12 @@
         <v>38</v>
       </c>
       <c r="H63" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C64">
         <v>140140</v>
@@ -1697,12 +1836,12 @@
         <v>40</v>
       </c>
       <c r="H64" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>140150</v>
@@ -1711,326 +1850,332 @@
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C66">
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="H66" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C67">
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="H67" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C68">
-        <v>140180</v>
+        <v>140200</v>
       </c>
       <c r="D68" t="s">
-        <v>68</v>
+        <v>58</v>
+      </c>
+      <c r="F68" t="s">
+        <v>70</v>
+      </c>
+      <c r="G68" t="s">
+        <v>72</v>
       </c>
       <c r="H68" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C69">
-        <v>140190</v>
+        <v>140210</v>
       </c>
       <c r="D69" t="s">
-        <v>69</v>
+        <v>59</v>
+      </c>
+      <c r="F69" t="s">
+        <v>70</v>
+      </c>
+      <c r="G69" t="s">
+        <v>72</v>
       </c>
       <c r="H69" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C70">
-        <v>140200</v>
+        <v>140220</v>
       </c>
       <c r="D70" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G70" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H70" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C71">
-        <v>140210</v>
+        <v>140221</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="F71" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G71" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H71" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C72">
-        <v>140220</v>
+        <v>140230</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
-      </c>
-      <c r="F72" t="s">
-        <v>75</v>
-      </c>
-      <c r="G72" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="H72" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C73">
-        <v>140230</v>
+        <v>140240</v>
       </c>
       <c r="D73" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="F73" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73" t="s">
+        <v>71</v>
       </c>
       <c r="H73" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C74">
-        <v>140240</v>
+        <v>140250</v>
       </c>
       <c r="D74" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F74" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G74" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H74" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C75">
-        <v>140250</v>
+        <v>140260</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
-      </c>
-      <c r="F75" t="s">
-        <v>74</v>
-      </c>
-      <c r="G75" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="H75" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C76">
-        <v>140260</v>
+        <v>140270</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="H76" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C77">
-        <v>140270</v>
+        <v>140280</v>
       </c>
       <c r="D77" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="H77" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C78">
-        <v>140280</v>
+        <v>140290</v>
       </c>
       <c r="D78" t="s">
         <v>62</v>
       </c>
       <c r="H78" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C79">
-        <v>140290</v>
+        <v>140300</v>
       </c>
       <c r="D79" t="s">
         <v>63</v>
       </c>
       <c r="H79" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C80">
-        <v>140300</v>
+        <v>140310</v>
       </c>
       <c r="D80" t="s">
         <v>64</v>
       </c>
       <c r="H80" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C81">
-        <v>140310</v>
+        <v>140320</v>
       </c>
       <c r="D81" t="s">
-        <v>65</v>
+        <v>76</v>
+      </c>
+      <c r="F81" t="s">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s">
+        <v>78</v>
       </c>
       <c r="H81" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C82">
-        <v>140320</v>
+        <v>140330</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
-      </c>
-      <c r="F82" t="s">
-        <v>82</v>
-      </c>
-      <c r="G82" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83">
+        <v>140340</v>
+      </c>
+      <c r="D83" t="s">
         <v>79</v>
       </c>
-      <c r="C83">
-        <v>140330</v>
-      </c>
-      <c r="D83" t="s">
-        <v>80</v>
-      </c>
       <c r="H83" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C84">
-        <v>140340</v>
+        <v>140350</v>
       </c>
       <c r="D84" t="s">
-        <v>84</v>
+        <v>96</v>
+      </c>
+      <c r="F84" t="s">
+        <v>98</v>
+      </c>
+      <c r="G84" t="s">
+        <v>100</v>
       </c>
       <c r="H84" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C85">
-        <v>140350</v>
+        <v>140360</v>
       </c>
       <c r="D85" t="s">
-        <v>101</v>
-      </c>
-      <c r="F85" t="s">
-        <v>103</v>
-      </c>
-      <c r="G85" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H85" t="s">
         <v>90</v>
@@ -2038,33 +2183,33 @@
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C86">
-        <v>140360</v>
+        <v>140370</v>
       </c>
       <c r="D86" t="s">
-        <v>102</v>
+        <v>94</v>
+      </c>
+      <c r="F86" t="s">
+        <v>99</v>
+      </c>
+      <c r="G86" t="s">
+        <v>101</v>
       </c>
       <c r="H86" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C87">
-        <v>140370</v>
+        <v>140380</v>
       </c>
       <c r="D87" t="s">
-        <v>99</v>
-      </c>
-      <c r="F87" t="s">
-        <v>104</v>
-      </c>
-      <c r="G87" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H87" t="s">
         <v>90</v>
@@ -2072,27 +2217,27 @@
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C88">
-        <v>140380</v>
+        <v>140390</v>
       </c>
       <c r="D88" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="C89">
-        <v>140390</v>
+        <v>141000</v>
       </c>
       <c r="D89" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="H89" t="s">
         <v>90</v>
@@ -2100,13 +2245,13 @@
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C90">
-        <v>200040</v>
+        <v>141010</v>
       </c>
       <c r="D90" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="H90" t="s">
         <v>90</v>
@@ -2114,16 +2259,504 @@
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C91">
+        <v>141020</v>
+      </c>
+      <c r="D91" t="s">
+        <v>113</v>
+      </c>
+      <c r="H91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92">
+        <v>141030</v>
+      </c>
+      <c r="D92" t="s">
+        <v>109</v>
+      </c>
+      <c r="H92" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93">
+        <v>141040</v>
+      </c>
+      <c r="D93" t="s">
+        <v>110</v>
+      </c>
+      <c r="H93" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94">
+        <v>141050</v>
+      </c>
+      <c r="D94" t="s">
+        <v>111</v>
+      </c>
+      <c r="H94" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95">
+        <v>141060</v>
+      </c>
+      <c r="D95" t="s">
+        <v>112</v>
+      </c>
+      <c r="H95" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B96" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96">
+        <v>141070</v>
+      </c>
+      <c r="D96" t="s">
+        <v>114</v>
+      </c>
+      <c r="H96" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B97" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97">
+        <v>141080</v>
+      </c>
+      <c r="D97" t="s">
+        <v>117</v>
+      </c>
+      <c r="H97" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B98" t="s">
+        <v>106</v>
+      </c>
+      <c r="C98">
+        <v>141081</v>
+      </c>
+      <c r="D98" t="s">
+        <v>129</v>
+      </c>
+      <c r="H98" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B99" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99">
+        <v>141082</v>
+      </c>
+      <c r="D99" t="s">
+        <v>130</v>
+      </c>
+      <c r="H99" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B100" t="s">
+        <v>106</v>
+      </c>
+      <c r="C100">
+        <v>141083</v>
+      </c>
+      <c r="D100" t="s">
+        <v>131</v>
+      </c>
+      <c r="H100" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B101" t="s">
+        <v>106</v>
+      </c>
+      <c r="C101">
+        <v>141084</v>
+      </c>
+      <c r="D101" t="s">
+        <v>132</v>
+      </c>
+      <c r="H101" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102">
+        <v>141090</v>
+      </c>
+      <c r="D102" t="s">
+        <v>118</v>
+      </c>
+      <c r="H102" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B103" t="s">
+        <v>106</v>
+      </c>
+      <c r="C103">
+        <v>141091</v>
+      </c>
+      <c r="D103" t="s">
+        <v>133</v>
+      </c>
+      <c r="H103" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B104" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104">
+        <v>141092</v>
+      </c>
+      <c r="D104" t="s">
+        <v>134</v>
+      </c>
+      <c r="H104" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105">
+        <v>141093</v>
+      </c>
+      <c r="D105" t="s">
+        <v>135</v>
+      </c>
+      <c r="H105" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B106" t="s">
+        <v>106</v>
+      </c>
+      <c r="C106">
+        <v>141094</v>
+      </c>
+      <c r="D106" t="s">
+        <v>136</v>
+      </c>
+      <c r="H106" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B107" t="s">
+        <v>106</v>
+      </c>
+      <c r="C107">
+        <v>141095</v>
+      </c>
+      <c r="D107" t="s">
+        <v>137</v>
+      </c>
+      <c r="H107" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
+        <v>106</v>
+      </c>
+      <c r="C108">
+        <v>141096</v>
+      </c>
+      <c r="D108" t="s">
+        <v>138</v>
+      </c>
+      <c r="H108" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B109" t="s">
+        <v>106</v>
+      </c>
+      <c r="C109">
+        <v>141100</v>
+      </c>
+      <c r="D109" t="s">
+        <v>119</v>
+      </c>
+      <c r="H109" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B110" t="s">
+        <v>106</v>
+      </c>
+      <c r="C110">
+        <v>141110</v>
+      </c>
+      <c r="D110" t="s">
+        <v>120</v>
+      </c>
+      <c r="H110" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
+        <v>106</v>
+      </c>
+      <c r="C111">
+        <v>141120</v>
+      </c>
+      <c r="D111" t="s">
+        <v>121</v>
+      </c>
+      <c r="H111" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>106</v>
+      </c>
+      <c r="C112">
+        <v>141130</v>
+      </c>
+      <c r="D112" t="s">
+        <v>122</v>
+      </c>
+      <c r="H112" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B113" t="s">
+        <v>106</v>
+      </c>
+      <c r="C113">
+        <v>141131</v>
+      </c>
+      <c r="D113" t="s">
+        <v>128</v>
+      </c>
+      <c r="H113" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B114" t="s">
+        <v>106</v>
+      </c>
+      <c r="C114">
+        <v>141140</v>
+      </c>
+      <c r="D114" t="s">
+        <v>123</v>
+      </c>
+      <c r="H114" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>106</v>
+      </c>
+      <c r="C115">
+        <v>141150</v>
+      </c>
+      <c r="D115" t="s">
+        <v>124</v>
+      </c>
+      <c r="H115" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B116" t="s">
+        <v>106</v>
+      </c>
+      <c r="C116">
+        <v>141160</v>
+      </c>
+      <c r="D116" t="s">
+        <v>125</v>
+      </c>
+      <c r="H116" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B117" t="s">
+        <v>106</v>
+      </c>
+      <c r="C117">
+        <v>141170</v>
+      </c>
+      <c r="D117" t="s">
+        <v>127</v>
+      </c>
+      <c r="H117" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>106</v>
+      </c>
+      <c r="C118">
+        <v>141180</v>
+      </c>
+      <c r="D118" t="s">
+        <v>139</v>
+      </c>
+      <c r="H118" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B119" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119">
+        <v>141190</v>
+      </c>
+      <c r="D119" t="s">
+        <v>140</v>
+      </c>
+      <c r="F119" t="s">
+        <v>69</v>
+      </c>
+      <c r="G119" t="s">
+        <v>71</v>
+      </c>
+      <c r="H119" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B120" t="s">
+        <v>106</v>
+      </c>
+      <c r="C120">
+        <v>141200</v>
+      </c>
+      <c r="D120" t="s">
+        <v>141</v>
+      </c>
+      <c r="F120" t="s">
+        <v>69</v>
+      </c>
+      <c r="G120" t="s">
+        <v>71</v>
+      </c>
+      <c r="H120" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B121" t="s">
+        <v>106</v>
+      </c>
+      <c r="C121">
+        <v>141210</v>
+      </c>
+      <c r="D121" t="s">
+        <v>126</v>
+      </c>
+      <c r="H121" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B122" t="s">
+        <v>106</v>
+      </c>
+      <c r="C122">
+        <v>141220</v>
+      </c>
+      <c r="D122" t="s">
+        <v>115</v>
+      </c>
+      <c r="H122" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B123" t="s">
+        <v>106</v>
+      </c>
+      <c r="C123">
+        <v>141230</v>
+      </c>
+      <c r="D123" t="s">
+        <v>116</v>
+      </c>
+      <c r="H123" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B124" t="s">
+        <v>83</v>
+      </c>
+      <c r="C124">
+        <v>200040</v>
+      </c>
+      <c r="D124" t="s">
+        <v>84</v>
+      </c>
+      <c r="H124" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B125" t="s">
+        <v>83</v>
+      </c>
+      <c r="C125">
         <v>200050</v>
       </c>
-      <c r="D91" t="s">
-        <v>91</v>
-      </c>
-      <c r="H91" t="s">
-        <v>92</v>
+      <c r="D125" t="s">
+        <v>86</v>
+      </c>
+      <c r="H125" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1236406-4F44-4556-B7B8-C10C9A5553D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66090833-0C9F-442A-B700-36F13A7F784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="151">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -316,10 +316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>提尔锋感染</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -332,10 +328,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -546,6 +538,46 @@
   </si>
   <si>
     <t>Attack_ExSpecial_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParryAid_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParryAid_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParryAid_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParryAid_H_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ParryAid_L_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssultAid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击_3</t>
+  </si>
+  <si>
+    <t>攻击_4</t>
+  </si>
+  <si>
+    <t>攻击_5</t>
+  </si>
+  <si>
+    <t>攻击_6</t>
+  </si>
+  <si>
+    <t>侵蚀提尔锋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -910,7 +942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="29.375" customWidth="1"/>
@@ -1010,7 +1042,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1024,7 +1056,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1038,7 +1070,7 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1052,7 +1084,7 @@
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1066,7 +1098,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1080,7 +1112,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1094,7 +1126,7 @@
         <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1108,7 +1140,7 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1122,7 +1154,7 @@
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1136,7 +1168,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1150,7 +1182,7 @@
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1164,7 +1196,7 @@
         <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -1178,7 +1210,7 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1192,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1206,7 +1238,7 @@
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1220,7 +1252,7 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1234,7 +1266,7 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1248,7 +1280,7 @@
         <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -1262,7 +1294,7 @@
         <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -1276,7 +1308,7 @@
         <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -1290,7 +1322,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -1304,7 +1336,7 @@
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -1318,7 +1350,7 @@
         <v>37</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -1332,7 +1364,7 @@
         <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -1346,7 +1378,7 @@
         <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -1360,7 +1392,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -1374,7 +1406,7 @@
         <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -1388,7 +1420,7 @@
         <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -1402,7 +1434,7 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -1416,7 +1448,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -1430,7 +1462,7 @@
         <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -1444,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -1458,7 +1490,7 @@
         <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -1472,7 +1504,7 @@
         <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -1486,7 +1518,7 @@
         <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -1500,7 +1532,7 @@
         <v>43</v>
       </c>
       <c r="H40" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -1514,7 +1546,7 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -1528,7 +1560,7 @@
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
@@ -1542,7 +1574,7 @@
         <v>46</v>
       </c>
       <c r="H43" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -1556,7 +1588,7 @@
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -1570,7 +1602,7 @@
         <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -1584,7 +1616,7 @@
         <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
@@ -1598,7 +1630,7 @@
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -1612,7 +1644,7 @@
         <v>37</v>
       </c>
       <c r="H48" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -1626,7 +1658,7 @@
         <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
@@ -1640,7 +1672,7 @@
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
@@ -1654,7 +1686,7 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -1668,7 +1700,7 @@
         <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
@@ -1682,7 +1714,7 @@
         <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
@@ -1696,7 +1728,7 @@
         <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
@@ -1710,7 +1742,7 @@
         <v>51</v>
       </c>
       <c r="H55" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
@@ -1724,7 +1756,7 @@
         <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
@@ -1738,7 +1770,7 @@
         <v>39</v>
       </c>
       <c r="H57" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
@@ -1752,7 +1784,7 @@
         <v>53</v>
       </c>
       <c r="H58" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
@@ -1766,7 +1798,7 @@
         <v>54</v>
       </c>
       <c r="H59" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
@@ -1780,7 +1812,7 @@
         <v>47</v>
       </c>
       <c r="H60" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
@@ -1794,7 +1826,7 @@
         <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
@@ -1808,7 +1840,7 @@
         <v>37</v>
       </c>
       <c r="H62" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
@@ -1822,7 +1854,7 @@
         <v>38</v>
       </c>
       <c r="H63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
@@ -1836,7 +1868,7 @@
         <v>40</v>
       </c>
       <c r="H64" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
@@ -1850,7 +1882,7 @@
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
@@ -1861,10 +1893,10 @@
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
@@ -1875,10 +1907,10 @@
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H67" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
@@ -1898,7 +1930,7 @@
         <v>72</v>
       </c>
       <c r="H68" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
@@ -1918,7 +1950,7 @@
         <v>72</v>
       </c>
       <c r="H69" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
@@ -1929,7 +1961,7 @@
         <v>140220</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F70" t="s">
         <v>70</v>
@@ -1938,7 +1970,7 @@
         <v>72</v>
       </c>
       <c r="H70" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
@@ -1949,7 +1981,7 @@
         <v>140221</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F71" t="s">
         <v>70</v>
@@ -1958,7 +1990,7 @@
         <v>72</v>
       </c>
       <c r="H71" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
@@ -1972,7 +2004,7 @@
         <v>45</v>
       </c>
       <c r="H72" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
@@ -1992,7 +2024,7 @@
         <v>71</v>
       </c>
       <c r="H73" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
@@ -2012,7 +2044,7 @@
         <v>71</v>
       </c>
       <c r="H74" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.2">
@@ -2026,7 +2058,7 @@
         <v>49</v>
       </c>
       <c r="H75" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
@@ -2040,7 +2072,7 @@
         <v>57</v>
       </c>
       <c r="H76" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
@@ -2054,7 +2086,7 @@
         <v>61</v>
       </c>
       <c r="H77" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.2">
@@ -2068,7 +2100,7 @@
         <v>62</v>
       </c>
       <c r="H78" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.2">
@@ -2082,7 +2114,7 @@
         <v>63</v>
       </c>
       <c r="H79" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.2">
@@ -2096,7 +2128,7 @@
         <v>64</v>
       </c>
       <c r="H80" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
@@ -2116,7 +2148,7 @@
         <v>78</v>
       </c>
       <c r="H81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
@@ -2130,7 +2162,7 @@
         <v>75</v>
       </c>
       <c r="H82" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
@@ -2144,7 +2176,7 @@
         <v>79</v>
       </c>
       <c r="H83" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
@@ -2155,16 +2187,16 @@
         <v>140350</v>
       </c>
       <c r="D84" t="s">
+        <v>94</v>
+      </c>
+      <c r="F84" t="s">
         <v>96</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>98</v>
       </c>
-      <c r="G84" t="s">
-        <v>100</v>
-      </c>
       <c r="H84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
@@ -2175,10 +2207,10 @@
         <v>140360</v>
       </c>
       <c r="D85" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H85" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
@@ -2189,16 +2221,16 @@
         <v>140370</v>
       </c>
       <c r="D86" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F86" t="s">
+        <v>97</v>
+      </c>
+      <c r="G86" t="s">
         <v>99</v>
       </c>
-      <c r="G86" t="s">
-        <v>101</v>
-      </c>
       <c r="H86" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
@@ -2209,10 +2241,10 @@
         <v>140380</v>
       </c>
       <c r="D87" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
@@ -2223,441 +2255,441 @@
         <v>140390</v>
       </c>
       <c r="D88" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C89">
         <v>141000</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H89" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C90">
         <v>141010</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H90" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C91">
         <v>141020</v>
       </c>
       <c r="D91" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H91" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C92">
         <v>141030</v>
       </c>
       <c r="D92" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H92" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C93">
         <v>141040</v>
       </c>
       <c r="D93" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C94">
         <v>141050</v>
       </c>
       <c r="D94" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H94" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C95">
         <v>141060</v>
       </c>
       <c r="D95" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H95" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C96">
         <v>141070</v>
       </c>
       <c r="D96" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H96" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C97">
         <v>141080</v>
       </c>
       <c r="D97" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H97" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C98">
         <v>141081</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H98" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C99">
         <v>141082</v>
       </c>
       <c r="D99" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H99" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C100">
         <v>141083</v>
       </c>
       <c r="D100" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H100" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C101">
         <v>141084</v>
       </c>
       <c r="D101" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H101" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C102">
         <v>141090</v>
       </c>
       <c r="D102" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H102" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C103">
         <v>141091</v>
       </c>
       <c r="D103" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H103" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C104">
         <v>141092</v>
       </c>
       <c r="D104" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H104" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C105">
         <v>141093</v>
       </c>
       <c r="D105" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H105" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C106">
         <v>141094</v>
       </c>
       <c r="D106" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H106" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C107">
         <v>141095</v>
       </c>
       <c r="D107" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H107" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C108">
         <v>141096</v>
       </c>
       <c r="D108" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H108" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C109">
         <v>141100</v>
       </c>
       <c r="D109" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H109" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C110">
         <v>141110</v>
       </c>
       <c r="D110" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H110" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C111">
         <v>141120</v>
       </c>
       <c r="D111" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H111" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C112">
         <v>141130</v>
       </c>
       <c r="D112" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H112" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C113">
         <v>141131</v>
       </c>
       <c r="D113" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H113" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C114">
         <v>141140</v>
       </c>
       <c r="D114" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H114" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C115">
         <v>141150</v>
       </c>
       <c r="D115" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H115" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C116">
         <v>141160</v>
       </c>
       <c r="D116" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H116" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C117">
         <v>141170</v>
       </c>
       <c r="D117" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H117" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="118" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C118">
         <v>141180</v>
       </c>
       <c r="D118" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H118" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="119" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C119">
         <v>141190</v>
       </c>
       <c r="D119" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F119" t="s">
         <v>69</v>
@@ -2666,18 +2698,18 @@
         <v>71</v>
       </c>
       <c r="H119" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C120">
         <v>141200</v>
       </c>
       <c r="D120" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F120" t="s">
         <v>69</v>
@@ -2686,77 +2718,229 @@
         <v>71</v>
       </c>
       <c r="H120" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="121" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C121">
         <v>141210</v>
       </c>
       <c r="D121" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H121" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="122" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C122">
         <v>141220</v>
       </c>
       <c r="D122" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H122" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="123" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C123">
         <v>141230</v>
       </c>
       <c r="D123" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H123" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C124">
-        <v>200040</v>
+        <v>141240</v>
       </c>
       <c r="D124" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="H124" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
+        <v>104</v>
+      </c>
+      <c r="C125">
+        <v>141250</v>
+      </c>
+      <c r="D125" t="s">
+        <v>141</v>
+      </c>
+      <c r="F125" t="s">
+        <v>97</v>
+      </c>
+      <c r="G125" t="s">
+        <v>99</v>
+      </c>
+      <c r="H125" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B126" t="s">
+        <v>104</v>
+      </c>
+      <c r="C126">
+        <v>141260</v>
+      </c>
+      <c r="D126" t="s">
+        <v>142</v>
+      </c>
+      <c r="F126" t="s">
+        <v>96</v>
+      </c>
+      <c r="G126" t="s">
+        <v>98</v>
+      </c>
+      <c r="H126" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B127" t="s">
+        <v>104</v>
+      </c>
+      <c r="C127">
+        <v>141270</v>
+      </c>
+      <c r="D127" t="s">
+        <v>143</v>
+      </c>
+      <c r="H127" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128">
+        <v>141280</v>
+      </c>
+      <c r="D128" t="s">
+        <v>144</v>
+      </c>
+      <c r="H128" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B129" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129">
+        <v>141290</v>
+      </c>
+      <c r="D129" t="s">
+        <v>145</v>
+      </c>
+      <c r="H129" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B130" t="s">
+        <v>150</v>
+      </c>
+      <c r="C130">
+        <v>200040</v>
+      </c>
+      <c r="D130" t="s">
         <v>83</v>
       </c>
-      <c r="C125">
+      <c r="H130" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B131" t="s">
+        <v>150</v>
+      </c>
+      <c r="C131">
         <v>200050</v>
       </c>
-      <c r="D125" t="s">
-        <v>86</v>
-      </c>
-      <c r="H125" t="s">
-        <v>87</v>
+      <c r="D131" t="s">
+        <v>85</v>
+      </c>
+      <c r="H131" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B132" t="s">
+        <v>150</v>
+      </c>
+      <c r="C132">
+        <v>200060</v>
+      </c>
+      <c r="D132" t="s">
+        <v>146</v>
+      </c>
+      <c r="H132" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B133" t="s">
+        <v>150</v>
+      </c>
+      <c r="C133">
+        <v>200070</v>
+      </c>
+      <c r="D133" t="s">
+        <v>147</v>
+      </c>
+      <c r="H133" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B134" t="s">
+        <v>150</v>
+      </c>
+      <c r="C134">
+        <v>200080</v>
+      </c>
+      <c r="D134" t="s">
+        <v>148</v>
+      </c>
+      <c r="H134" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B135" t="s">
+        <v>150</v>
+      </c>
+      <c r="C135">
+        <v>200090</v>
+      </c>
+      <c r="D135" t="s">
+        <v>149</v>
+      </c>
+      <c r="H135" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66090833-0C9F-442A-B700-36F13A7F784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935D04E6-C01E-46F2-A700-6C6E49BDF42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="166">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -316,18 +316,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5,99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -565,19 +557,86 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_3</t>
-  </si>
-  <si>
-    <t>攻击_4</t>
-  </si>
-  <si>
-    <t>攻击_5</t>
-  </si>
-  <si>
-    <t>攻击_6</t>
-  </si>
-  <si>
     <t>侵蚀提尔锋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Attack_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Attack_02</t>
+  </si>
+  <si>
+    <t>TryfingInfested_Attack_03</t>
+  </si>
+  <si>
+    <t>TryfingInfested_Attack_04</t>
+  </si>
+  <si>
+    <t>TryfingInfested_Attack_05</t>
+  </si>
+  <si>
+    <t>TryfingInfested_Attack_06</t>
+  </si>
+  <si>
+    <t>TryfingInfested_Run_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Run_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Run_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Walk_B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Walk_F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Walk_F_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Walk_F_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Walk_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Walk_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Hit_Front_Up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Hit_Shake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Stun_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Stun_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TryfingInfested_Stun_End</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -942,9 +1001,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
     <col min="4" max="4" width="29.375" customWidth="1"/>
     <col min="5" max="5" width="39.625" customWidth="1"/>
     <col min="6" max="6" width="41.875" customWidth="1"/>
@@ -1042,7 +1102,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1056,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1070,7 +1130,7 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1084,7 +1144,7 @@
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1098,7 +1158,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1112,7 +1172,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1126,7 +1186,7 @@
         <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1140,7 +1200,7 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1154,7 +1214,7 @@
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1168,7 +1228,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1182,7 +1242,7 @@
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1196,7 +1256,7 @@
         <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -1210,7 +1270,7 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1224,7 +1284,7 @@
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1238,7 +1298,7 @@
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1252,7 +1312,7 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1266,7 +1326,7 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1280,7 +1340,7 @@
         <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -1294,7 +1354,7 @@
         <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -1308,7 +1368,7 @@
         <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -1322,7 +1382,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -1336,7 +1396,7 @@
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -1350,7 +1410,7 @@
         <v>37</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -1364,7 +1424,7 @@
         <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -1378,7 +1438,7 @@
         <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -1392,7 +1452,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -1406,7 +1466,7 @@
         <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -1420,7 +1480,7 @@
         <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -1434,7 +1494,7 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -1448,7 +1508,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -1462,7 +1522,7 @@
         <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -1476,7 +1536,7 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -1490,7 +1550,7 @@
         <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -1504,7 +1564,7 @@
         <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -1518,7 +1578,7 @@
         <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -1532,7 +1592,7 @@
         <v>43</v>
       </c>
       <c r="H40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -1546,7 +1606,7 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -1560,7 +1620,7 @@
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
@@ -1574,7 +1634,7 @@
         <v>46</v>
       </c>
       <c r="H43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -1588,7 +1648,7 @@
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -1602,7 +1662,7 @@
         <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -1616,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
@@ -1630,7 +1690,7 @@
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -1644,7 +1704,7 @@
         <v>37</v>
       </c>
       <c r="H48" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -1658,7 +1718,7 @@
         <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
@@ -1672,7 +1732,7 @@
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
@@ -1686,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -1700,7 +1760,7 @@
         <v>17</v>
       </c>
       <c r="H52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
@@ -1714,7 +1774,7 @@
         <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
@@ -1728,7 +1788,7 @@
         <v>50</v>
       </c>
       <c r="H54" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
@@ -1742,7 +1802,7 @@
         <v>51</v>
       </c>
       <c r="H55" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
@@ -1756,7 +1816,7 @@
         <v>52</v>
       </c>
       <c r="H56" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
@@ -1770,7 +1830,7 @@
         <v>39</v>
       </c>
       <c r="H57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
@@ -1784,7 +1844,7 @@
         <v>53</v>
       </c>
       <c r="H58" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
@@ -1798,7 +1858,7 @@
         <v>54</v>
       </c>
       <c r="H59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
@@ -1812,7 +1872,7 @@
         <v>47</v>
       </c>
       <c r="H60" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
@@ -1826,7 +1886,7 @@
         <v>48</v>
       </c>
       <c r="H61" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
@@ -1840,7 +1900,7 @@
         <v>37</v>
       </c>
       <c r="H62" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
@@ -1854,7 +1914,7 @@
         <v>38</v>
       </c>
       <c r="H63" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
@@ -1868,7 +1928,7 @@
         <v>40</v>
       </c>
       <c r="H64" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
@@ -1882,7 +1942,7 @@
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
@@ -1893,10 +1953,10 @@
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
@@ -1907,10 +1967,10 @@
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H67" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
@@ -1930,7 +1990,7 @@
         <v>72</v>
       </c>
       <c r="H68" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
@@ -1950,7 +2010,7 @@
         <v>72</v>
       </c>
       <c r="H69" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
@@ -1961,7 +2021,7 @@
         <v>140220</v>
       </c>
       <c r="D70" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F70" t="s">
         <v>70</v>
@@ -1970,7 +2030,7 @@
         <v>72</v>
       </c>
       <c r="H70" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
@@ -1981,7 +2041,7 @@
         <v>140221</v>
       </c>
       <c r="D71" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F71" t="s">
         <v>70</v>
@@ -1990,7 +2050,7 @@
         <v>72</v>
       </c>
       <c r="H71" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
@@ -2004,7 +2064,7 @@
         <v>45</v>
       </c>
       <c r="H72" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
@@ -2024,7 +2084,7 @@
         <v>71</v>
       </c>
       <c r="H73" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
@@ -2044,7 +2104,7 @@
         <v>71</v>
       </c>
       <c r="H74" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.2">
@@ -2058,7 +2118,7 @@
         <v>49</v>
       </c>
       <c r="H75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
@@ -2072,7 +2132,7 @@
         <v>57</v>
       </c>
       <c r="H76" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
@@ -2086,7 +2146,7 @@
         <v>61</v>
       </c>
       <c r="H77" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.2">
@@ -2100,7 +2160,7 @@
         <v>62</v>
       </c>
       <c r="H78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.2">
@@ -2114,7 +2174,7 @@
         <v>63</v>
       </c>
       <c r="H79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.2">
@@ -2128,7 +2188,7 @@
         <v>64</v>
       </c>
       <c r="H80" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
@@ -2148,7 +2208,7 @@
         <v>78</v>
       </c>
       <c r="H81" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
@@ -2162,7 +2222,7 @@
         <v>75</v>
       </c>
       <c r="H82" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
@@ -2176,7 +2236,7 @@
         <v>79</v>
       </c>
       <c r="H83" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
@@ -2187,16 +2247,16 @@
         <v>140350</v>
       </c>
       <c r="D84" t="s">
+        <v>92</v>
+      </c>
+      <c r="F84" t="s">
         <v>94</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>96</v>
       </c>
-      <c r="G84" t="s">
-        <v>98</v>
-      </c>
       <c r="H84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
@@ -2207,10 +2267,10 @@
         <v>140360</v>
       </c>
       <c r="D85" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
@@ -2221,16 +2281,16 @@
         <v>140370</v>
       </c>
       <c r="D86" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F86" t="s">
+        <v>95</v>
+      </c>
+      <c r="G86" t="s">
         <v>97</v>
       </c>
-      <c r="G86" t="s">
-        <v>99</v>
-      </c>
       <c r="H86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
@@ -2241,10 +2301,10 @@
         <v>140380</v>
       </c>
       <c r="D87" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
@@ -2255,441 +2315,441 @@
         <v>140390</v>
       </c>
       <c r="D88" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C89">
         <v>141000</v>
       </c>
       <c r="D89" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H89" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C90">
         <v>141010</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H90" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C91">
         <v>141020</v>
       </c>
       <c r="D91" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H91" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C92">
         <v>141030</v>
       </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H92" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C93">
         <v>141040</v>
       </c>
       <c r="D93" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C94">
         <v>141050</v>
       </c>
       <c r="D94" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H94" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C95">
         <v>141060</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H95" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C96">
         <v>141070</v>
       </c>
       <c r="D96" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H96" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C97">
         <v>141080</v>
       </c>
       <c r="D97" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H97" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C98">
         <v>141081</v>
       </c>
       <c r="D98" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H98" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C99">
         <v>141082</v>
       </c>
       <c r="D99" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H99" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C100">
         <v>141083</v>
       </c>
       <c r="D100" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H100" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C101">
         <v>141084</v>
       </c>
       <c r="D101" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H101" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C102">
         <v>141090</v>
       </c>
       <c r="D102" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H102" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C103">
         <v>141091</v>
       </c>
       <c r="D103" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H103" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C104">
         <v>141092</v>
       </c>
       <c r="D104" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H104" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C105">
         <v>141093</v>
       </c>
       <c r="D105" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="H105" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C106">
         <v>141094</v>
       </c>
       <c r="D106" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H106" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C107">
         <v>141095</v>
       </c>
       <c r="D107" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H107" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C108">
         <v>141096</v>
       </c>
       <c r="D108" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H108" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C109">
         <v>141100</v>
       </c>
       <c r="D109" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H109" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C110">
         <v>141110</v>
       </c>
       <c r="D110" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H110" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C111">
         <v>141120</v>
       </c>
       <c r="D111" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H111" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C112">
         <v>141130</v>
       </c>
       <c r="D112" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H112" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C113">
         <v>141131</v>
       </c>
       <c r="D113" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H113" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C114">
         <v>141140</v>
       </c>
       <c r="D114" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C115">
         <v>141150</v>
       </c>
       <c r="D115" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H115" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C116">
         <v>141160</v>
       </c>
       <c r="D116" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H116" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C117">
         <v>141170</v>
       </c>
       <c r="D117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H117" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C118">
         <v>141180</v>
       </c>
       <c r="D118" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H118" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C119">
         <v>141190</v>
       </c>
       <c r="D119" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F119" t="s">
         <v>69</v>
@@ -2698,18 +2758,18 @@
         <v>71</v>
       </c>
       <c r="H119" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="120" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C120">
         <v>141200</v>
       </c>
       <c r="D120" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F120" t="s">
         <v>69</v>
@@ -2718,229 +2778,439 @@
         <v>71</v>
       </c>
       <c r="H120" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="121" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C121">
         <v>141210</v>
       </c>
       <c r="D121" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H121" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C122">
         <v>141220</v>
       </c>
       <c r="D122" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H122" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="123" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C123">
         <v>141230</v>
       </c>
       <c r="D123" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H123" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C124">
         <v>141240</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H124" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C125">
         <v>141250</v>
       </c>
       <c r="D125" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F125" t="s">
+        <v>95</v>
+      </c>
+      <c r="G125" t="s">
         <v>97</v>
       </c>
-      <c r="G125" t="s">
-        <v>99</v>
-      </c>
       <c r="H125" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C126">
         <v>141260</v>
       </c>
       <c r="D126" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F126" t="s">
+        <v>94</v>
+      </c>
+      <c r="G126" t="s">
         <v>96</v>
       </c>
-      <c r="G126" t="s">
-        <v>98</v>
-      </c>
       <c r="H126" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C127">
         <v>141270</v>
       </c>
       <c r="D127" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H127" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="128" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C128">
         <v>141280</v>
       </c>
       <c r="D128" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H128" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="129" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B129" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C129">
         <v>141290</v>
       </c>
       <c r="D129" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H129" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C130">
-        <v>200040</v>
+        <v>200010</v>
       </c>
       <c r="D130" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="H130" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C131">
-        <v>200050</v>
+        <v>200020</v>
       </c>
       <c r="D131" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="H131" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C132">
-        <v>200060</v>
+        <v>200021</v>
       </c>
       <c r="D132" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H132" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C133">
-        <v>200070</v>
+        <v>200022</v>
       </c>
       <c r="D133" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="H133" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C134">
-        <v>200080</v>
+        <v>200030</v>
       </c>
       <c r="D134" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H134" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B135" t="s">
+        <v>144</v>
+      </c>
+      <c r="C135">
+        <v>200031</v>
+      </c>
+      <c r="D135" t="s">
+        <v>156</v>
+      </c>
+      <c r="H135" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B136" t="s">
+        <v>144</v>
+      </c>
+      <c r="C136">
+        <v>200032</v>
+      </c>
+      <c r="D136" t="s">
+        <v>157</v>
+      </c>
+      <c r="H136" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B137" t="s">
+        <v>144</v>
+      </c>
+      <c r="C137">
+        <v>200033</v>
+      </c>
+      <c r="D137" t="s">
+        <v>158</v>
+      </c>
+      <c r="H137" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B138" t="s">
+        <v>144</v>
+      </c>
+      <c r="C138">
+        <v>200034</v>
+      </c>
+      <c r="D138" t="s">
+        <v>159</v>
+      </c>
+      <c r="H138" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B139" t="s">
+        <v>144</v>
+      </c>
+      <c r="C139">
+        <v>200035</v>
+      </c>
+      <c r="D139" t="s">
+        <v>160</v>
+      </c>
+      <c r="H139" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B140" t="s">
+        <v>144</v>
+      </c>
+      <c r="C140">
+        <v>200040</v>
+      </c>
+      <c r="D140" t="s">
+        <v>146</v>
+      </c>
+      <c r="H140" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>144</v>
+      </c>
+      <c r="C141">
+        <v>200050</v>
+      </c>
+      <c r="D141" t="s">
+        <v>147</v>
+      </c>
+      <c r="H141" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>144</v>
+      </c>
+      <c r="C142">
+        <v>200060</v>
+      </c>
+      <c r="D142" t="s">
+        <v>148</v>
+      </c>
+      <c r="H142" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>144</v>
+      </c>
+      <c r="C143">
+        <v>200070</v>
+      </c>
+      <c r="D143" t="s">
+        <v>149</v>
+      </c>
+      <c r="H143" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B144" t="s">
+        <v>144</v>
+      </c>
+      <c r="C144">
+        <v>200080</v>
+      </c>
+      <c r="D144" t="s">
         <v>150</v>
       </c>
-      <c r="C135">
+      <c r="H144" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B145" t="s">
+        <v>144</v>
+      </c>
+      <c r="C145">
         <v>200090</v>
       </c>
-      <c r="D135" t="s">
-        <v>149</v>
-      </c>
-      <c r="H135" t="s">
-        <v>90</v>
+      <c r="D145" t="s">
+        <v>151</v>
+      </c>
+      <c r="H145" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B146" t="s">
+        <v>144</v>
+      </c>
+      <c r="C146">
+        <v>200100</v>
+      </c>
+      <c r="D146" t="s">
+        <v>161</v>
+      </c>
+      <c r="H146" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B147" t="s">
+        <v>144</v>
+      </c>
+      <c r="C147">
+        <v>200101</v>
+      </c>
+      <c r="D147" t="s">
+        <v>162</v>
+      </c>
+      <c r="H147" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B148" t="s">
+        <v>144</v>
+      </c>
+      <c r="C148">
+        <v>200120</v>
+      </c>
+      <c r="D148" t="s">
+        <v>163</v>
+      </c>
+      <c r="H148" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B149" t="s">
+        <v>144</v>
+      </c>
+      <c r="C149">
+        <v>200121</v>
+      </c>
+      <c r="D149" t="s">
+        <v>164</v>
+      </c>
+      <c r="H149" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B150" t="s">
+        <v>144</v>
+      </c>
+      <c r="C150">
+        <v>200122</v>
+      </c>
+      <c r="D150" t="s">
+        <v>165</v>
+      </c>
+      <c r="H150" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935D04E6-C01E-46F2-A700-6C6E49BDF42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A5856-D70B-43B1-AA4E-049454CB7ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="168">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -334,10 +334,6 @@
     <t>5,0</t>
   </si>
   <si>
-    <t>5,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击_招架反击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -637,6 +633,17 @@
   </si>
   <si>
     <t>TryfingInfested_Stun_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>5,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1928,7 +1935,7 @@
         <v>40</v>
       </c>
       <c r="H64" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
@@ -1942,7 +1949,7 @@
         <v>41</v>
       </c>
       <c r="H65" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
@@ -1953,7 +1960,7 @@
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H66" t="s">
         <v>87</v>
@@ -1967,7 +1974,7 @@
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H67" t="s">
         <v>87</v>
@@ -1990,7 +1997,7 @@
         <v>72</v>
       </c>
       <c r="H68" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
@@ -2010,7 +2017,7 @@
         <v>72</v>
       </c>
       <c r="H69" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
@@ -2021,7 +2028,7 @@
         <v>140220</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F70" t="s">
         <v>70</v>
@@ -2041,7 +2048,7 @@
         <v>140221</v>
       </c>
       <c r="D71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F71" t="s">
         <v>70</v>
@@ -2118,7 +2125,7 @@
         <v>49</v>
       </c>
       <c r="H75" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
@@ -2132,7 +2139,7 @@
         <v>57</v>
       </c>
       <c r="H76" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
@@ -2247,13 +2254,13 @@
         <v>140350</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F84" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G84" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H84" t="s">
         <v>83</v>
@@ -2267,7 +2274,7 @@
         <v>140360</v>
       </c>
       <c r="D85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H85" t="s">
         <v>84</v>
@@ -2281,13 +2288,13 @@
         <v>140370</v>
       </c>
       <c r="D86" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F86" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G86" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H86" t="s">
         <v>83</v>
@@ -2301,7 +2308,7 @@
         <v>140380</v>
       </c>
       <c r="D87" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s">
         <v>84</v>
@@ -2315,7 +2322,7 @@
         <v>140390</v>
       </c>
       <c r="D88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s">
         <v>83</v>
@@ -2323,13 +2330,13 @@
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C89">
         <v>141000</v>
       </c>
       <c r="D89" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H89" t="s">
         <v>86</v>
@@ -2337,13 +2344,13 @@
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C90">
         <v>141010</v>
       </c>
       <c r="D90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H90" t="s">
         <v>86</v>
@@ -2351,13 +2358,13 @@
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C91">
         <v>141020</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H91" t="s">
         <v>85</v>
@@ -2365,13 +2372,13 @@
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C92">
         <v>141030</v>
       </c>
       <c r="D92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H92" t="s">
         <v>85</v>
@@ -2379,13 +2386,13 @@
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C93">
         <v>141040</v>
       </c>
       <c r="D93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H93" t="s">
         <v>85</v>
@@ -2393,13 +2400,13 @@
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C94">
         <v>141050</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H94" t="s">
         <v>85</v>
@@ -2407,13 +2414,13 @@
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C95">
         <v>141060</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H95" t="s">
         <v>85</v>
@@ -2421,13 +2428,13 @@
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C96">
         <v>141070</v>
       </c>
       <c r="D96" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H96" t="s">
         <v>85</v>
@@ -2435,13 +2442,13 @@
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C97">
         <v>141080</v>
       </c>
       <c r="D97" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H97" t="s">
         <v>85</v>
@@ -2449,13 +2456,13 @@
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C98">
         <v>141081</v>
       </c>
       <c r="D98" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H98" t="s">
         <v>85</v>
@@ -2463,13 +2470,13 @@
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C99">
         <v>141082</v>
       </c>
       <c r="D99" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H99" t="s">
         <v>85</v>
@@ -2477,13 +2484,13 @@
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C100">
         <v>141083</v>
       </c>
       <c r="D100" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H100" t="s">
         <v>85</v>
@@ -2491,13 +2498,13 @@
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C101">
         <v>141084</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H101" t="s">
         <v>85</v>
@@ -2505,13 +2512,13 @@
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C102">
         <v>141090</v>
       </c>
       <c r="D102" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H102" t="s">
         <v>85</v>
@@ -2519,13 +2526,13 @@
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C103">
         <v>141091</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H103" t="s">
         <v>85</v>
@@ -2533,13 +2540,13 @@
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C104">
         <v>141092</v>
       </c>
       <c r="D104" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H104" t="s">
         <v>85</v>
@@ -2547,13 +2554,13 @@
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C105">
         <v>141093</v>
       </c>
       <c r="D105" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H105" t="s">
         <v>85</v>
@@ -2561,13 +2568,13 @@
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C106">
         <v>141094</v>
       </c>
       <c r="D106" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H106" t="s">
         <v>85</v>
@@ -2575,13 +2582,13 @@
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C107">
         <v>141095</v>
       </c>
       <c r="D107" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H107" t="s">
         <v>85</v>
@@ -2589,13 +2596,13 @@
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C108">
         <v>141096</v>
       </c>
       <c r="D108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H108" t="s">
         <v>85</v>
@@ -2603,41 +2610,41 @@
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C109">
         <v>141100</v>
       </c>
       <c r="D109" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H109" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C110">
         <v>141110</v>
       </c>
       <c r="D110" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H110" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C111">
         <v>141120</v>
       </c>
       <c r="D111" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H111" t="s">
         <v>87</v>
@@ -2645,41 +2652,41 @@
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C112">
         <v>141130</v>
       </c>
       <c r="D112" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H112" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C113">
         <v>141131</v>
       </c>
       <c r="D113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H113" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C114">
         <v>141140</v>
       </c>
       <c r="D114" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H114" t="s">
         <v>87</v>
@@ -2687,13 +2694,13 @@
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C115">
         <v>141150</v>
       </c>
       <c r="D115" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H115" t="s">
         <v>87</v>
@@ -2701,13 +2708,13 @@
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C116">
         <v>141160</v>
       </c>
       <c r="D116" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H116" t="s">
         <v>87</v>
@@ -2715,13 +2722,13 @@
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C117">
         <v>141170</v>
       </c>
       <c r="D117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H117" t="s">
         <v>87</v>
@@ -2729,13 +2736,13 @@
     </row>
     <row r="118" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C118">
         <v>141180</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H118" t="s">
         <v>87</v>
@@ -2743,13 +2750,13 @@
     </row>
     <row r="119" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C119">
         <v>141190</v>
       </c>
       <c r="D119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F119" t="s">
         <v>69</v>
@@ -2763,13 +2770,13 @@
     </row>
     <row r="120" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C120">
         <v>141200</v>
       </c>
       <c r="D120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F120" t="s">
         <v>69</v>
@@ -2783,27 +2790,27 @@
     </row>
     <row r="121" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C121">
         <v>141210</v>
       </c>
       <c r="D121" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H121" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
     </row>
     <row r="122" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C122">
         <v>141220</v>
       </c>
       <c r="D122" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H122" t="s">
         <v>85</v>
@@ -2811,13 +2818,13 @@
     </row>
     <row r="123" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C123">
         <v>141230</v>
       </c>
       <c r="D123" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H123" t="s">
         <v>85</v>
@@ -2825,13 +2832,13 @@
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C124">
         <v>141240</v>
       </c>
       <c r="D124" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H124" t="s">
         <v>84</v>
@@ -2839,19 +2846,19 @@
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C125">
         <v>141250</v>
       </c>
       <c r="D125" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F125" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G125" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H125" t="s">
         <v>83</v>
@@ -2859,19 +2866,19 @@
     </row>
     <row r="126" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C126">
         <v>141260</v>
       </c>
       <c r="D126" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F126" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G126" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H126" t="s">
         <v>83</v>
@@ -2879,13 +2886,13 @@
     </row>
     <row r="127" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C127">
         <v>141270</v>
       </c>
       <c r="D127" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H127" t="s">
         <v>84</v>
@@ -2893,13 +2900,13 @@
     </row>
     <row r="128" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C128">
         <v>141280</v>
       </c>
       <c r="D128" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H128" t="s">
         <v>84</v>
@@ -2907,13 +2914,13 @@
     </row>
     <row r="129" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B129" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C129">
         <v>141290</v>
       </c>
       <c r="D129" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H129" t="s">
         <v>83</v>
@@ -2921,13 +2928,13 @@
     </row>
     <row r="130" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C130">
         <v>200010</v>
       </c>
       <c r="D130" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H130" t="s">
         <v>85</v>
@@ -2935,13 +2942,13 @@
     </row>
     <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C131">
         <v>200020</v>
       </c>
       <c r="D131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H131" t="s">
         <v>85</v>
@@ -2949,13 +2956,13 @@
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C132">
         <v>200021</v>
       </c>
       <c r="D132" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H132" t="s">
         <v>85</v>
@@ -2963,13 +2970,13 @@
     </row>
     <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C133">
         <v>200022</v>
       </c>
       <c r="D133" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H133" t="s">
         <v>85</v>
@@ -2977,13 +2984,13 @@
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C134">
         <v>200030</v>
       </c>
       <c r="D134" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H134" t="s">
         <v>85</v>
@@ -2991,13 +2998,13 @@
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B135" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C135">
         <v>200031</v>
       </c>
       <c r="D135" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H135" t="s">
         <v>85</v>
@@ -3005,13 +3012,13 @@
     </row>
     <row r="136" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B136" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C136">
         <v>200032</v>
       </c>
       <c r="D136" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H136" t="s">
         <v>85</v>
@@ -3019,13 +3026,13 @@
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C137">
         <v>200033</v>
       </c>
       <c r="D137" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H137" t="s">
         <v>85</v>
@@ -3033,13 +3040,13 @@
     </row>
     <row r="138" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C138">
         <v>200034</v>
       </c>
       <c r="D138" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H138" t="s">
         <v>85</v>
@@ -3047,13 +3054,13 @@
     </row>
     <row r="139" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B139" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C139">
         <v>200035</v>
       </c>
       <c r="D139" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H139" t="s">
         <v>85</v>
@@ -3061,97 +3068,97 @@
     </row>
     <row r="140" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C140">
         <v>200040</v>
       </c>
       <c r="D140" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H140" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
     </row>
     <row r="141" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C141">
         <v>200050</v>
       </c>
       <c r="D141" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H141" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
     </row>
     <row r="142" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C142">
         <v>200060</v>
       </c>
       <c r="D142" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H142" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
     </row>
     <row r="143" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C143">
         <v>200070</v>
       </c>
       <c r="D143" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H143" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
     </row>
     <row r="144" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C144">
         <v>200080</v>
       </c>
       <c r="D144" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H144" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B145" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C145">
         <v>200090</v>
       </c>
       <c r="D145" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H145" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C146">
         <v>200100</v>
       </c>
       <c r="D146" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H146" t="s">
         <v>85</v>
@@ -3159,13 +3166,13 @@
     </row>
     <row r="147" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B147" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C147">
         <v>200101</v>
       </c>
       <c r="D147" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H147" t="s">
         <v>85</v>
@@ -3173,44 +3180,44 @@
     </row>
     <row r="148" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B148" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C148">
         <v>200120</v>
       </c>
       <c r="D148" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H148" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="149" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C149">
         <v>200121</v>
       </c>
       <c r="D149" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H149" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B150" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C150">
         <v>200122</v>
       </c>
       <c r="D150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H150" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058A5856-D70B-43B1-AA4E-049454CB7ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FCA4A5-5143-42BA-AA54-172803AB9111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="181">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,60 +190,10 @@
     <t>攻击_冲刺攻击</t>
   </si>
   <si>
-    <t>基础_特殊冲刺</t>
-  </si>
-  <si>
-    <t>基础_慢跑停止</t>
-  </si>
-  <si>
-    <t>基础_冲刺停止</t>
-  </si>
-  <si>
-    <t>基础_特殊冲刺起步_前</t>
-  </si>
-  <si>
-    <t>基础_特殊冲刺起步_后</t>
-  </si>
-  <si>
-    <t>攻击_特殊技_2_强化</t>
-  </si>
-  <si>
     <t>#Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_冲刺攻击_急冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_1_急冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_2_急冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_特殊技_3_急冻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_特殊冲刺攻击_蓄力前摇</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_特殊冲刺攻击_蓄力前摇_快蓄</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_特殊冲刺攻击_无蓄力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_特殊冲刺攻击_蓄力</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(list),ZZZ.AttributeCondition</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,14 +234,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_普通攻击_霜降</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_冰刃浪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Ellen_FlashFreeze,GreaterEqual,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -300,10 +242,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_招架支援_Start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.ActionResilience</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -334,26 +272,6 @@
     <t>5,0</t>
   </si>
   <si>
-    <t>攻击_招架反击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_招架支援_重</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_招架支援_重_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_招架支援_轻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_招架支援_轻_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AssistPoint,GreaterEqual,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -370,272 +288,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻击_普通攻击_3_近</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3_远</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3_急冻_近</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3_急冻_远</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>青衣</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Walk_Start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Walk_Loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Walk_Start_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Walk_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Run_Loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Walk_Start2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Run_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SwitchIn_Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SwitchOut_Normal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Front</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Back</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Normal_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Normal_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Normal_04</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Normal_05</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Normal_06</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Normal_07</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Branch_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Rush</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Branch_02</t>
-  </si>
-  <si>
-    <t>Attack_Normal_05_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Front_Left</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Front_LeftFoot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Front_Right</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Front_RightFoot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Back_Left</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Back_LeftFoot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Back_Right</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Back_RightFoot</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Left</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Evade_Right</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Special</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_ExSpecial</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_ExSpecial_02</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ParryAid_Start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ParryAid_H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ParryAid_L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ParryAid_H_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ParryAid_L_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AssultAid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>侵蚀提尔锋</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TryfingInfested_Idle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Attack_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Attack_02</t>
-  </si>
-  <si>
-    <t>TryfingInfested_Attack_03</t>
-  </si>
-  <si>
-    <t>TryfingInfested_Attack_04</t>
-  </si>
-  <si>
-    <t>TryfingInfested_Attack_05</t>
-  </si>
-  <si>
-    <t>TryfingInfested_Attack_06</t>
-  </si>
-  <si>
-    <t>TryfingInfested_Run_Loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Run_Start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Run_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Walk_B</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Walk_F</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Walk_F_L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Walk_F_R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Walk_L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Walk_R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Hit_Front_Up</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Hit_Shake</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Stun_Start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Stun_Loop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TryfingInfested_Stun_End</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5,5</t>
   </si>
   <si>
@@ -644,6 +304,371 @@
   </si>
   <si>
     <t>2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Walk_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Walk_Start2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Walk_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Walk_Start_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Walk_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Run_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Run_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Front</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Front_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Front_LeftFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Front_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Front_RightFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Back_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Back_LeftFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Back_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Back_RightFoot</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Left</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Evade_Right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_05_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Normal_07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Branch_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Branch_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_ExSpecial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_ExSpecial_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_Attack_Rush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_SwitchIn_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_SwitchOut_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_H_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_ParryAid_L_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QingYi_AssultAid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Walk_Start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Walk_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Run_Loop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Walk_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Run_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Walk_Start_End</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Evade_Front</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Evade_Back</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_SwitchIn_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_SwitchOut_Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Rush</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Rush_Ex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Branch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Branch_Ex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Branch_Ex_Enhanced</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_Enhanced_Card</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_ParryAid_Start</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_ParryAid_L</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_ParryAid_L_End</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_ParryAid_H_End</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Idle</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Run_Start</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Run_Loop</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Run_End</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Walk_F_L</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Walk_F_R</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Walk_L</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Walk_R</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Attack_01</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Attack_02</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Attack_03</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Attack_04</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Attack_05</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Attack_06</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Hit_Front_Up</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Hit_Shake</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Stun_Start</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Stun_Loop</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Stun_End</t>
+  </si>
+  <si>
+    <t>TyrfingInfested_Walk_F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TyrfingInfested_Walk_B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Loop_01</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Start_Front</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Start_Back</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Slash_01</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Slash_01_Fast</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Cut_01_Fast</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Dash_Cut_01</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_01</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_02</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_03_Near</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_03</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_01_Ex</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_02_Ex</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_03_Ex_Near</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_01_03_Ex</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_Normal_02_345</t>
+  </si>
+  <si>
+    <t>Ellen_Attack_ParryAid_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_Attack_AssultAid_Near</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1023,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1035,13 +1060,13 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="G1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="H1" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1058,13 +1083,13 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="H2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1089,13 +1114,13 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1109,7 +1134,7 @@
         <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1123,7 +1148,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1137,7 +1162,7 @@
         <v>17</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1151,7 +1176,7 @@
         <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1165,7 +1190,7 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1179,7 +1204,7 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1193,7 +1218,7 @@
         <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1207,7 +1232,7 @@
         <v>22</v>
       </c>
       <c r="H12" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1221,7 +1246,7 @@
         <v>23</v>
       </c>
       <c r="H13" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1235,7 +1260,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1249,7 +1274,7 @@
         <v>25</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1263,7 +1288,7 @@
         <v>26</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -1277,7 +1302,7 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1291,7 +1316,7 @@
         <v>28</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1305,7 +1330,7 @@
         <v>29</v>
       </c>
       <c r="H19" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1319,7 +1344,7 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1333,7 +1358,7 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1347,7 +1372,7 @@
         <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
@@ -1361,7 +1386,7 @@
         <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -1375,7 +1400,7 @@
         <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -1389,7 +1414,7 @@
         <v>35</v>
       </c>
       <c r="H25" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
@@ -1403,7 +1428,7 @@
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -1417,7 +1442,7 @@
         <v>37</v>
       </c>
       <c r="H27" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -1431,7 +1456,7 @@
         <v>38</v>
       </c>
       <c r="H28" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -1445,7 +1470,7 @@
         <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -1459,7 +1484,7 @@
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -1473,7 +1498,7 @@
         <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -1487,7 +1512,7 @@
         <v>17</v>
       </c>
       <c r="H32" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -1501,7 +1526,7 @@
         <v>19</v>
       </c>
       <c r="H33" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -1515,7 +1540,7 @@
         <v>20</v>
       </c>
       <c r="H34" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -1529,7 +1554,7 @@
         <v>39</v>
       </c>
       <c r="H35" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -1543,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -1557,7 +1582,7 @@
         <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
@@ -1571,7 +1596,7 @@
         <v>41</v>
       </c>
       <c r="H38" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
@@ -1585,7 +1610,7 @@
         <v>42</v>
       </c>
       <c r="H39" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -1599,7 +1624,7 @@
         <v>43</v>
       </c>
       <c r="H40" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -1613,7 +1638,7 @@
         <v>44</v>
       </c>
       <c r="H41" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
@@ -1627,7 +1652,7 @@
         <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
@@ -1641,7 +1666,7 @@
         <v>46</v>
       </c>
       <c r="H43" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -1655,7 +1680,7 @@
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -1669,7 +1694,7 @@
         <v>47</v>
       </c>
       <c r="H45" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -1683,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="H46" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
@@ -1697,7 +1722,7 @@
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -1711,7 +1736,7 @@
         <v>37</v>
       </c>
       <c r="H48" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -1725,1499 +1750,1499 @@
         <v>38</v>
       </c>
       <c r="H49" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C50">
         <v>140000</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="H50" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C51">
         <v>140010</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="H51" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C52">
         <v>140020</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>123</v>
       </c>
       <c r="H52" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C53">
         <v>140030</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="H53" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C54">
         <v>140040</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="H54" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C55">
         <v>140050</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="H55" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C56">
         <v>140060</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="H56" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C57">
         <v>140070</v>
       </c>
       <c r="D57" t="s">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="H57" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C58">
         <v>140080</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="H58" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C59">
         <v>140090</v>
       </c>
       <c r="D59" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="H59" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C60">
         <v>140100</v>
       </c>
       <c r="D60" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="H60" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C61">
         <v>140110</v>
       </c>
       <c r="D61" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="H61" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C62">
         <v>140120</v>
       </c>
       <c r="D62" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="H62" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C63">
         <v>140130</v>
       </c>
       <c r="D63" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="H63" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C64">
         <v>140140</v>
       </c>
       <c r="D64" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="H64" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C65">
         <v>140150</v>
       </c>
       <c r="D65" t="s">
-        <v>41</v>
+        <v>171</v>
       </c>
       <c r="H65" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C66">
         <v>140160</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="H66" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C67">
         <v>140170</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="H67" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C68">
         <v>140200</v>
       </c>
       <c r="D68" t="s">
+        <v>174</v>
+      </c>
+      <c r="F68" t="s">
+        <v>56</v>
+      </c>
+      <c r="G68" t="s">
         <v>58</v>
       </c>
-      <c r="F68" t="s">
-        <v>70</v>
-      </c>
-      <c r="G68" t="s">
-        <v>72</v>
-      </c>
       <c r="H68" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C69">
         <v>140210</v>
       </c>
       <c r="D69" t="s">
-        <v>59</v>
+        <v>175</v>
       </c>
       <c r="F69" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="G69" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="H69" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C70">
         <v>140220</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="F70" t="s">
+        <v>56</v>
+      </c>
+      <c r="G70" t="s">
+        <v>58</v>
+      </c>
+      <c r="H70" t="s">
         <v>70</v>
-      </c>
-      <c r="G70" t="s">
-        <v>72</v>
-      </c>
-      <c r="H70" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C71">
         <v>140221</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>177</v>
       </c>
       <c r="F71" t="s">
+        <v>56</v>
+      </c>
+      <c r="G71" t="s">
+        <v>58</v>
+      </c>
+      <c r="H71" t="s">
         <v>70</v>
-      </c>
-      <c r="G71" t="s">
-        <v>72</v>
-      </c>
-      <c r="H71" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C72">
         <v>140230</v>
       </c>
       <c r="D72" t="s">
-        <v>45</v>
+        <v>134</v>
       </c>
       <c r="H72" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C73">
         <v>140240</v>
       </c>
       <c r="D73" t="s">
+        <v>135</v>
+      </c>
+      <c r="F73" t="s">
         <v>55</v>
       </c>
-      <c r="F73" t="s">
-        <v>69</v>
-      </c>
       <c r="G73" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="H73" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C74">
         <v>140250</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="F74" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="H74" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C75">
         <v>140260</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="H75" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C76">
         <v>140270</v>
       </c>
       <c r="D76" t="s">
-        <v>57</v>
+        <v>133</v>
       </c>
       <c r="H76" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C77">
         <v>140280</v>
       </c>
       <c r="D77" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="H77" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C78">
         <v>140290</v>
       </c>
       <c r="D78" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="H78" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C79">
         <v>140300</v>
       </c>
       <c r="D79" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="H79" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C80">
         <v>140310</v>
       </c>
       <c r="D80" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="H80" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C81">
         <v>140320</v>
       </c>
       <c r="D81" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G81" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="H81" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C82">
         <v>140330</v>
       </c>
       <c r="D82" t="s">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="H82" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C83">
         <v>140340</v>
       </c>
       <c r="D83" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="H83" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C84">
         <v>140350</v>
       </c>
       <c r="D84" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="F84" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="G84" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H84" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C85">
         <v>140360</v>
       </c>
       <c r="D85" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="H85" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C86">
         <v>140370</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>179</v>
       </c>
       <c r="F86" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G86" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H86" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C87">
         <v>140380</v>
       </c>
       <c r="D87" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="H87" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C88">
         <v>140390</v>
       </c>
       <c r="D88" t="s">
-        <v>88</v>
+        <v>180</v>
       </c>
       <c r="H88" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C89">
         <v>141000</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C90">
         <v>141010</v>
       </c>
       <c r="D90" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C91">
         <v>141020</v>
       </c>
       <c r="D91" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C92">
         <v>141030</v>
       </c>
       <c r="D92" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="H92" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C93">
         <v>141040</v>
       </c>
       <c r="D93" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="H93" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C94">
         <v>141050</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="H94" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C95">
         <v>141060</v>
       </c>
       <c r="D95" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="H95" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C96">
         <v>141070</v>
       </c>
       <c r="D96" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="H96" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C97">
         <v>141080</v>
       </c>
       <c r="D97" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C98">
         <v>141081</v>
       </c>
       <c r="D98" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="H98" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C99">
         <v>141082</v>
       </c>
       <c r="D99" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="H99" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C100">
         <v>141083</v>
       </c>
       <c r="D100" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="H100" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C101">
         <v>141084</v>
       </c>
       <c r="D101" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="H101" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C102">
         <v>141090</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="H102" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C103">
         <v>141091</v>
       </c>
       <c r="D103" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="H103" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C104">
         <v>141092</v>
       </c>
       <c r="D104" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="H104" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C105">
         <v>141093</v>
       </c>
       <c r="D105" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="H105" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C106">
         <v>141094</v>
       </c>
       <c r="D106" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="H106" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B107" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C107">
         <v>141095</v>
       </c>
       <c r="D107" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="H107" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B108" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C108">
         <v>141096</v>
       </c>
       <c r="D108" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="H108" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C109">
         <v>141100</v>
       </c>
       <c r="D109" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="H109" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B110" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C110">
         <v>141110</v>
       </c>
       <c r="D110" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="H110" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B111" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C111">
         <v>141120</v>
       </c>
       <c r="D111" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="H111" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B112" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C112">
         <v>141130</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="H112" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="113" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C113">
         <v>141131</v>
       </c>
       <c r="D113" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="H113" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C114">
         <v>141140</v>
       </c>
       <c r="D114" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="H114" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B115" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C115">
         <v>141150</v>
       </c>
       <c r="D115" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H115" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C116">
         <v>141160</v>
       </c>
       <c r="D116" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="H116" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B117" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C117">
         <v>141170</v>
       </c>
       <c r="D117" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="H117" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B118" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C118">
         <v>141180</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="H118" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B119" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C119">
         <v>141190</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="F119" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G119" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="H119" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B120" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C120">
         <v>141200</v>
       </c>
       <c r="D120" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="F120" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G120" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="H120" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B121" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C121">
         <v>141210</v>
       </c>
       <c r="D121" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H121" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="122" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C122">
         <v>141220</v>
       </c>
       <c r="D122" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="H122" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="123" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B123" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C123">
         <v>141230</v>
       </c>
       <c r="D123" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H123" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="124" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B124" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C124">
         <v>141240</v>
       </c>
       <c r="D124" t="s">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="H124" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B125" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C125">
         <v>141250</v>
       </c>
       <c r="D125" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F125" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="G125" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="H125" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B126" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C126">
         <v>141260</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="F126" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="G126" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="H126" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="127" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C127">
         <v>141270</v>
       </c>
       <c r="D127" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="H127" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="128" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C128">
         <v>141280</v>
       </c>
       <c r="D128" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="H128" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B129" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C129">
         <v>141290</v>
       </c>
       <c r="D129" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H129" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
     </row>
     <row r="130" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C130">
         <v>200010</v>
       </c>
       <c r="D130" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H130" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="131" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C131">
         <v>200020</v>
       </c>
       <c r="D131" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="H131" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C132">
         <v>200021</v>
       </c>
       <c r="D132" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H132" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="133" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C133">
         <v>200022</v>
       </c>
       <c r="D133" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H133" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C134">
         <v>200030</v>
       </c>
       <c r="D134" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H134" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B135" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C135">
         <v>200031</v>
       </c>
       <c r="D135" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H135" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B136" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C136">
         <v>200032</v>
       </c>
       <c r="D136" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H136" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B137" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C137">
         <v>200033</v>
       </c>
       <c r="D137" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H137" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B138" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C138">
         <v>200034</v>
       </c>
       <c r="D138" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="H138" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="139" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B139" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C139">
         <v>200035</v>
       </c>
       <c r="D139" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="H139" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="140" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C140">
         <v>200040</v>
       </c>
       <c r="D140" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H140" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="141" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B141" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C141">
         <v>200050</v>
       </c>
       <c r="D141" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H141" t="s">
-        <v>166</v>
+        <v>78</v>
       </c>
     </row>
     <row r="142" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B142" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C142">
         <v>200060</v>
       </c>
       <c r="D142" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="H142" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="143" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B143" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C143">
         <v>200070</v>
       </c>
       <c r="D143" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H143" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B144" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C144">
         <v>200080</v>
       </c>
       <c r="D144" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H144" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="145" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B145" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C145">
         <v>200090</v>
       </c>
       <c r="D145" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="H145" t="s">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="146" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B146" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C146">
         <v>200100</v>
       </c>
       <c r="D146" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H146" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="147" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B147" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C147">
         <v>200101</v>
       </c>
       <c r="D147" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H147" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="148" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B148" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C148">
         <v>200120</v>
       </c>
       <c r="D148" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H148" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="149" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C149">
         <v>200121</v>
       </c>
       <c r="D149" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H149" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="150" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B150" t="s">
-        <v>143</v>
+        <v>76</v>
       </c>
       <c r="C150">
         <v>200122</v>
       </c>
       <c r="D150" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H150" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/#ZZZ.Skill.xlsx
+++ b/Configs/Datas/#ZZZ.Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FCA4A5-5143-42BA-AA54-172803AB9111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D8EED3-F67A-4218-84E2-772F4ADFA2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="146">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -79,117 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>安比</t>
-  </si>
-  <si>
-    <t>星见雅</t>
-  </si>
-  <si>
-    <t>基础_待机</t>
-  </si>
-  <si>
-    <t>基础_慢跑起步</t>
-  </si>
-  <si>
-    <t>基础_慢跑</t>
-  </si>
-  <si>
-    <t>基础_冲刺起步</t>
-  </si>
-  <si>
-    <t>基础_冲刺</t>
-  </si>
-  <si>
-    <t>基础_停止</t>
-  </si>
-  <si>
-    <t>基础_急停转向</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击1</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击2</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击3</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击4</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击4_落雷</t>
-  </si>
-  <si>
-    <t>攻击_特殊技</t>
-  </si>
-  <si>
-    <t>攻击_特殊技_快速</t>
-  </si>
-  <si>
-    <t>攻击_强化特殊技</t>
-  </si>
-  <si>
-    <t>攻击_强化特殊技_快速</t>
-  </si>
-  <si>
-    <t>攻击_终极技</t>
-  </si>
-  <si>
-    <t>闪避_前</t>
-  </si>
-  <si>
-    <t>闪避_后</t>
-  </si>
-  <si>
-    <t>攻击_冲刺普攻</t>
-  </si>
-  <si>
-    <t>受击_轻_前</t>
-  </si>
-  <si>
-    <t>受击_重</t>
-  </si>
-  <si>
-    <t>切人_切入</t>
-  </si>
-  <si>
-    <t>切人_切出</t>
-  </si>
-  <si>
-    <t>基础_慢跑起步停止</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击_1</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击_2</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击_3</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击_4</t>
-  </si>
-  <si>
-    <t>攻击_普通攻击_5</t>
-  </si>
-  <si>
-    <t>攻击_特殊技_1</t>
-  </si>
-  <si>
-    <t>攻击_特殊技_1_无前摇</t>
-  </si>
-  <si>
-    <t>闪避_前_1</t>
-  </si>
-  <si>
-    <t>闪避_后_1</t>
-  </si>
-  <si>
-    <t>攻击_冲刺攻击</t>
-  </si>
-  <si>
     <t>#Remark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -269,9 +158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5,0</t>
-  </si>
-  <si>
     <t>AssistPoint,GreaterEqual,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -296,17 +182,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5,5</t>
-  </si>
-  <si>
-    <t>5,5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>QingYi_Idle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -669,6 +544,29 @@
   </si>
   <si>
     <t>Ellen_Attack_AssultAid_Near</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>2,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20,99</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -734,6 +632,22 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B7706215-2F9A-48A1-9F9B-AE648AC09887}" name="表1" displayName="表1" ref="B4:H105" totalsRowShown="0">
+  <autoFilter ref="B4:H105" xr:uid="{B7706215-2F9A-48A1-9F9B-AE648AC09887}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{86C7AD81-009B-4E64-9EA4-30CD954D8F1E}" name="角色名称"/>
+    <tableColumn id="2" xr3:uid="{7453514B-17AF-42E9-A892-0362B9528937}" name="id"/>
+    <tableColumn id="3" xr3:uid="{161FFD0F-F6E4-4D27-B7C5-A63C6DBF3AE4}" name="技能名称"/>
+    <tableColumn id="4" xr3:uid="{849D7EE4-76B2-4E21-A634-3EBF7613C5D1}" name="技能描述"/>
+    <tableColumn id="5" xr3:uid="{0E742351-C380-440B-A281-DCA439F51AB1}" name="技能条件"/>
+    <tableColumn id="6" xr3:uid="{817C76C3-99A5-4A50-9C0A-FEE30CD1211B}" name="技能消耗"/>
+    <tableColumn id="7" xr3:uid="{2ECCC692-848C-47A7-BF00-5C397AC96182}" name="韧性"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1033,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4CF470-E9E0-44FF-BA6C-71B5C42FB7B2}">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.25" customWidth="1"/>
@@ -1048,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1060,13 +974,13 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1083,13 +997,13 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1114,2139 +1028,1512 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>10000</v>
+        <v>140000</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="H5" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>10001</v>
+        <v>140010</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>10002</v>
+        <v>140020</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>10003</v>
+        <v>140030</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>10004</v>
+        <v>140040</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>122</v>
       </c>
       <c r="H9" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C10">
-        <v>10005</v>
+        <v>140050</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>10006</v>
+        <v>140060</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>10007</v>
+        <v>140070</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C13">
-        <v>10008</v>
+        <v>140080</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C14">
-        <v>10009</v>
+        <v>140090</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="H14" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>10010</v>
+        <v>140100</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C16">
-        <v>10011</v>
+        <v>140110</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>10012</v>
+        <v>140120</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C18">
-        <v>10013</v>
+        <v>140130</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="H18" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>10014</v>
+        <v>140140</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="H19" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C20">
-        <v>10015</v>
+        <v>140150</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C21">
-        <v>10016</v>
+        <v>140160</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="H21" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>10017</v>
+        <v>140170</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="H22" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>10018</v>
+        <v>140200</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>133</v>
+      </c>
+      <c r="F23" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" t="s">
+        <v>21</v>
       </c>
       <c r="H23" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>10019</v>
+        <v>140210</v>
       </c>
       <c r="D24" t="s">
-        <v>34</v>
+        <v>134</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
       </c>
       <c r="H24" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>10020</v>
+        <v>140220</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>135</v>
+      </c>
+      <c r="F25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
       </c>
       <c r="H25" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C26">
-        <v>10021</v>
+        <v>140221</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>136</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
       </c>
       <c r="H26" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C27">
-        <v>10022</v>
+        <v>140230</v>
       </c>
       <c r="D27" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C28">
-        <v>10023</v>
+        <v>140240</v>
       </c>
       <c r="D28" t="s">
-        <v>38</v>
+        <v>94</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
       </c>
       <c r="H28" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C29">
-        <v>10200</v>
+        <v>140250</v>
       </c>
       <c r="D29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" t="s">
         <v>18</v>
       </c>
+      <c r="G29" t="s">
+        <v>20</v>
+      </c>
       <c r="H29" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C30">
-        <v>10201</v>
+        <v>140260</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C31">
-        <v>10202</v>
+        <v>140270</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C32">
-        <v>10203</v>
+        <v>140280</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="H32" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C33">
-        <v>10204</v>
+        <v>140290</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="H33" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C34">
-        <v>10205</v>
+        <v>140300</v>
       </c>
       <c r="D34" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="H34" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C35">
-        <v>10206</v>
+        <v>140310</v>
       </c>
       <c r="D35" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C36">
-        <v>10207</v>
+        <v>140320</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>137</v>
+      </c>
+      <c r="F36" t="s">
+        <v>24</v>
+      </c>
+      <c r="G36" t="s">
+        <v>25</v>
       </c>
       <c r="H36" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C37">
-        <v>10208</v>
+        <v>140330</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="H37" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C38">
-        <v>10209</v>
+        <v>140340</v>
       </c>
       <c r="D38" t="s">
-        <v>41</v>
+        <v>97</v>
       </c>
       <c r="H38" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C39">
-        <v>10210</v>
+        <v>140350</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>98</v>
+      </c>
+      <c r="F39" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" t="s">
+        <v>35</v>
       </c>
       <c r="H39" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C40">
-        <v>10211</v>
+        <v>140360</v>
       </c>
       <c r="D40" t="s">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="H40" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C41">
-        <v>10212</v>
+        <v>140370</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>138</v>
+      </c>
+      <c r="F41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" t="s">
+        <v>36</v>
       </c>
       <c r="H41" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C42">
-        <v>10213</v>
+        <v>140380</v>
       </c>
       <c r="D42" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="H42" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C43">
-        <v>10214</v>
+        <v>140390</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>139</v>
       </c>
       <c r="H43" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C44">
-        <v>10215</v>
+        <v>141000</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H44" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C45">
-        <v>10216</v>
+        <v>141010</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H45" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C46">
-        <v>10217</v>
+        <v>141020</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H46" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C47">
-        <v>10218</v>
+        <v>141030</v>
       </c>
       <c r="D47" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H47" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C48">
-        <v>10219</v>
+        <v>141040</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H48" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C49">
-        <v>10220</v>
+        <v>141050</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H49" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C50">
-        <v>140000</v>
+        <v>141060</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="H50" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C51">
-        <v>140010</v>
+        <v>141070</v>
       </c>
       <c r="D51" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="H51" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C52">
-        <v>140020</v>
+        <v>141080</v>
       </c>
       <c r="D52" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C53">
-        <v>140030</v>
+        <v>141081</v>
       </c>
       <c r="D53" t="s">
-        <v>124</v>
+        <v>48</v>
       </c>
       <c r="H53" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C54">
-        <v>140040</v>
+        <v>141082</v>
       </c>
       <c r="D54" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="H54" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C55">
-        <v>140050</v>
+        <v>141083</v>
       </c>
       <c r="D55" t="s">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C56">
-        <v>140060</v>
+        <v>141084</v>
       </c>
       <c r="D56" t="s">
-        <v>126</v>
+        <v>51</v>
       </c>
       <c r="H56" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C57">
-        <v>140070</v>
+        <v>141090</v>
       </c>
       <c r="D57" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="H57" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C58">
-        <v>140080</v>
+        <v>141091</v>
       </c>
       <c r="D58" t="s">
-        <v>164</v>
+        <v>53</v>
       </c>
       <c r="H58" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C59">
-        <v>140090</v>
+        <v>141092</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="H59" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C60">
-        <v>140100</v>
+        <v>141093</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="H60" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C61">
-        <v>140110</v>
+        <v>141094</v>
       </c>
       <c r="D61" t="s">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="H61" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C62">
-        <v>140120</v>
+        <v>141095</v>
       </c>
       <c r="D62" t="s">
-        <v>130</v>
+        <v>57</v>
       </c>
       <c r="H62" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C63">
-        <v>140130</v>
+        <v>141096</v>
       </c>
       <c r="D63" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="H63" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C64">
-        <v>140140</v>
+        <v>141100</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="H64" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65">
+        <v>141110</v>
+      </c>
+      <c r="D65" t="s">
         <v>60</v>
       </c>
-      <c r="C65">
-        <v>140150</v>
-      </c>
-      <c r="D65" t="s">
-        <v>171</v>
-      </c>
       <c r="H65" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C66">
-        <v>140160</v>
+        <v>141120</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>61</v>
       </c>
       <c r="H66" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B67" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C67">
-        <v>140170</v>
+        <v>141130</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>62</v>
       </c>
       <c r="H67" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B68" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C68">
-        <v>140200</v>
+        <v>141131</v>
       </c>
       <c r="D68" t="s">
-        <v>174</v>
-      </c>
-      <c r="F68" t="s">
-        <v>56</v>
-      </c>
-      <c r="G68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H68" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C69">
-        <v>140210</v>
+        <v>141140</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
-      </c>
-      <c r="F69" t="s">
-        <v>56</v>
-      </c>
-      <c r="G69" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H69" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C70">
-        <v>140220</v>
+        <v>141150</v>
       </c>
       <c r="D70" t="s">
-        <v>176</v>
-      </c>
-      <c r="F70" t="s">
-        <v>56</v>
-      </c>
-      <c r="G70" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H70" t="s">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C71">
-        <v>140221</v>
+        <v>141160</v>
       </c>
       <c r="D71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F71" t="s">
-        <v>56</v>
-      </c>
-      <c r="G71" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H71" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C72">
-        <v>140230</v>
+        <v>141170</v>
       </c>
       <c r="D72" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="H72" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C73">
-        <v>140240</v>
+        <v>141180</v>
       </c>
       <c r="D73" t="s">
-        <v>135</v>
-      </c>
-      <c r="F73" t="s">
-        <v>55</v>
-      </c>
-      <c r="G73" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="H73" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B74" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C74">
-        <v>140250</v>
+        <v>141190</v>
       </c>
       <c r="D74" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="F74" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="G74" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="H74" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C75">
-        <v>140260</v>
+        <v>141200</v>
       </c>
       <c r="D75" t="s">
-        <v>132</v>
+        <v>70</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>20</v>
       </c>
       <c r="H75" t="s">
-        <v>79</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C76">
-        <v>140270</v>
+        <v>141210</v>
       </c>
       <c r="D76" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="H76" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B77" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C77">
-        <v>140280</v>
+        <v>141220</v>
       </c>
       <c r="D77" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="H77" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B78" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C78">
-        <v>140290</v>
+        <v>141230</v>
       </c>
       <c r="D78" t="s">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B79" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C79">
-        <v>140300</v>
+        <v>141240</v>
       </c>
       <c r="D79" t="s">
-        <v>168</v>
+        <v>74</v>
       </c>
       <c r="H79" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B80" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C80">
-        <v>140310</v>
+        <v>141250</v>
       </c>
       <c r="D80" t="s">
-        <v>169</v>
+        <v>75</v>
+      </c>
+      <c r="F80" t="s">
+        <v>34</v>
+      </c>
+      <c r="G80" t="s">
+        <v>36</v>
       </c>
       <c r="H80" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B81" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C81">
-        <v>140320</v>
+        <v>141260</v>
       </c>
       <c r="D81" t="s">
-        <v>178</v>
+        <v>76</v>
       </c>
       <c r="F81" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="G81" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="H81" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B82" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C82">
-        <v>140330</v>
+        <v>141270</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="H82" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B83" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C83">
-        <v>140340</v>
+        <v>141280</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="H83" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B84" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C84">
-        <v>140350</v>
+        <v>141290</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
-      </c>
-      <c r="F84" t="s">
-        <v>71</v>
-      </c>
-      <c r="G84" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B85" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C85">
-        <v>140360</v>
+        <v>200010</v>
       </c>
       <c r="D85" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="H85" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B86" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C86">
-        <v>140370</v>
+        <v>200020</v>
       </c>
       <c r="D86" t="s">
-        <v>179</v>
-      </c>
-      <c r="F86" t="s">
-        <v>72</v>
-      </c>
-      <c r="G86" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="H86" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B87" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C87">
-        <v>140380</v>
+        <v>200021</v>
       </c>
       <c r="D87" t="s">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="H87" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B88" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C88">
-        <v>140390</v>
+        <v>200022</v>
       </c>
       <c r="D88" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="H88" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B89" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C89">
-        <v>141000</v>
+        <v>200030</v>
       </c>
       <c r="D89" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H89" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B90" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C90">
-        <v>141010</v>
+        <v>200031</v>
       </c>
       <c r="D90" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="H90" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B91" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C91">
-        <v>141020</v>
+        <v>200032</v>
       </c>
       <c r="D91" t="s">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="H91" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B92" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C92">
-        <v>141030</v>
+        <v>200033</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="H92" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C93">
-        <v>141040</v>
+        <v>200034</v>
       </c>
       <c r="D93" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="H93" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C94">
-        <v>141050</v>
+        <v>200035</v>
       </c>
       <c r="D94" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="H94" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B95" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C95">
-        <v>141060</v>
+        <v>200040</v>
       </c>
       <c r="D95" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="H95" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B96" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C96">
-        <v>141070</v>
+        <v>200050</v>
       </c>
       <c r="D96" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="H96" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B97" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C97">
-        <v>141080</v>
+        <v>200060</v>
       </c>
       <c r="D97" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H97" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B98" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C98">
-        <v>141081</v>
+        <v>200070</v>
       </c>
       <c r="D98" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H98" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B99" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C99">
-        <v>141082</v>
+        <v>200080</v>
       </c>
       <c r="D99" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="H99" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="100" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B100" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C100">
-        <v>141083</v>
+        <v>200090</v>
       </c>
       <c r="D100" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="H100" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="101" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C101">
-        <v>141084</v>
+        <v>200100</v>
       </c>
       <c r="D101" t="s">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="H101" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C102">
-        <v>141090</v>
+        <v>200101</v>
       </c>
       <c r="D102" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="H102" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B103" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C103">
-        <v>141091</v>
+        <v>200120</v>
       </c>
       <c r="D103" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="H103" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B104" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C104">
-        <v>141092</v>
+        <v>200121</v>
       </c>
       <c r="D104" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="H104" t="s">
-        <v>68</v>
+        <v>140</v>
       </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B105" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C105">
-        <v>141093</v>
+        <v>200122</v>
       </c>
       <c r="D105" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="H105" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B106" t="s">
-        <v>75</v>
-      </c>
-      <c r="C106">
-        <v>141094</v>
-      </c>
-      <c r="D106" t="s">
-        <v>97</v>
-      </c>
-      <c r="H106" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B107" t="s">
-        <v>75</v>
-      </c>
-      <c r="C107">
-        <v>141095</v>
-      </c>
-      <c r="D107" t="s">
-        <v>98</v>
-      </c>
-      <c r="H107" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B108" t="s">
-        <v>75</v>
-      </c>
-      <c r="C108">
-        <v>141096</v>
-      </c>
-      <c r="D108" t="s">
-        <v>99</v>
-      </c>
-      <c r="H108" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B109" t="s">
-        <v>75</v>
-      </c>
-      <c r="C109">
-        <v>141100</v>
-      </c>
-      <c r="D109" t="s">
-        <v>100</v>
-      </c>
-      <c r="H109" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B110" t="s">
-        <v>75</v>
-      </c>
-      <c r="C110">
-        <v>141110</v>
-      </c>
-      <c r="D110" t="s">
-        <v>101</v>
-      </c>
-      <c r="H110" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B111" t="s">
-        <v>75</v>
-      </c>
-      <c r="C111">
-        <v>141120</v>
-      </c>
-      <c r="D111" t="s">
-        <v>102</v>
-      </c>
-      <c r="H111" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B112" t="s">
-        <v>75</v>
-      </c>
-      <c r="C112">
-        <v>141130</v>
-      </c>
-      <c r="D112" t="s">
-        <v>103</v>
-      </c>
-      <c r="H112" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B113" t="s">
-        <v>75</v>
-      </c>
-      <c r="C113">
-        <v>141131</v>
-      </c>
-      <c r="D113" t="s">
-        <v>104</v>
-      </c>
-      <c r="H113" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B114" t="s">
-        <v>75</v>
-      </c>
-      <c r="C114">
-        <v>141140</v>
-      </c>
-      <c r="D114" t="s">
-        <v>105</v>
-      </c>
-      <c r="H114" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B115" t="s">
-        <v>75</v>
-      </c>
-      <c r="C115">
-        <v>141150</v>
-      </c>
-      <c r="D115" t="s">
-        <v>106</v>
-      </c>
-      <c r="H115" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B116" t="s">
-        <v>75</v>
-      </c>
-      <c r="C116">
-        <v>141160</v>
-      </c>
-      <c r="D116" t="s">
-        <v>107</v>
-      </c>
-      <c r="H116" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B117" t="s">
-        <v>75</v>
-      </c>
-      <c r="C117">
-        <v>141170</v>
-      </c>
-      <c r="D117" t="s">
-        <v>108</v>
-      </c>
-      <c r="H117" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B118" t="s">
-        <v>75</v>
-      </c>
-      <c r="C118">
-        <v>141180</v>
-      </c>
-      <c r="D118" t="s">
-        <v>109</v>
-      </c>
-      <c r="H118" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B119" t="s">
-        <v>75</v>
-      </c>
-      <c r="C119">
-        <v>141190</v>
-      </c>
-      <c r="D119" t="s">
-        <v>110</v>
-      </c>
-      <c r="F119" t="s">
-        <v>55</v>
-      </c>
-      <c r="G119" t="s">
-        <v>57</v>
-      </c>
-      <c r="H119" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B120" t="s">
-        <v>75</v>
-      </c>
-      <c r="C120">
-        <v>141200</v>
-      </c>
-      <c r="D120" t="s">
-        <v>111</v>
-      </c>
-      <c r="F120" t="s">
-        <v>55</v>
-      </c>
-      <c r="G120" t="s">
-        <v>57</v>
-      </c>
-      <c r="H120" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B121" t="s">
-        <v>75</v>
-      </c>
-      <c r="C121">
-        <v>141210</v>
-      </c>
-      <c r="D121" t="s">
-        <v>112</v>
-      </c>
-      <c r="H121" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B122" t="s">
-        <v>75</v>
-      </c>
-      <c r="C122">
-        <v>141220</v>
-      </c>
-      <c r="D122" t="s">
-        <v>113</v>
-      </c>
-      <c r="H122" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B123" t="s">
-        <v>75</v>
-      </c>
-      <c r="C123">
-        <v>141230</v>
-      </c>
-      <c r="D123" t="s">
-        <v>114</v>
-      </c>
-      <c r="H123" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B124" t="s">
-        <v>75</v>
-      </c>
-      <c r="C124">
-        <v>141240</v>
-      </c>
-      <c r="D124" t="s">
-        <v>115</v>
-      </c>
-      <c r="H124" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B125" t="s">
-        <v>75</v>
-      </c>
-      <c r="C125">
-        <v>141250</v>
-      </c>
-      <c r="D125" t="s">
-        <v>116</v>
-      </c>
-      <c r="F125" t="s">
-        <v>72</v>
-      </c>
-      <c r="G125" t="s">
-        <v>74</v>
-      </c>
-      <c r="H125" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B126" t="s">
-        <v>75</v>
-      </c>
-      <c r="C126">
-        <v>141260</v>
-      </c>
-      <c r="D126" t="s">
-        <v>117</v>
-      </c>
-      <c r="F126" t="s">
-        <v>71</v>
-      </c>
-      <c r="G126" t="s">
-        <v>73</v>
-      </c>
-      <c r="H126" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B127" t="s">
-        <v>75</v>
-      </c>
-      <c r="C127">
-        <v>141270</v>
-      </c>
-      <c r="D127" t="s">
-        <v>118</v>
-      </c>
-      <c r="H127" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B128" t="s">
-        <v>75</v>
-      </c>
-      <c r="C128">
-        <v>141280</v>
-      </c>
-      <c r="D128" t="s">
-        <v>119</v>
-      </c>
-      <c r="H128" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B129" t="s">
-        <v>75</v>
-      </c>
-      <c r="C129">
-        <v>141290</v>
-      </c>
-      <c r="D129" t="s">
-        <v>120</v>
-      </c>
-      <c r="H129" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B130" t="s">
-        <v>76</v>
-      </c>
-      <c r="C130">
-        <v>200010</v>
-      </c>
-      <c r="D130" t="s">
-        <v>142</v>
-      </c>
-      <c r="H130" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B131" t="s">
-        <v>76</v>
-      </c>
-      <c r="C131">
-        <v>200020</v>
-      </c>
-      <c r="D131" t="s">
-        <v>143</v>
-      </c>
-      <c r="H131" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B132" t="s">
-        <v>76</v>
-      </c>
-      <c r="C132">
-        <v>200021</v>
-      </c>
-      <c r="D132" t="s">
-        <v>144</v>
-      </c>
-      <c r="H132" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B133" t="s">
-        <v>76</v>
-      </c>
-      <c r="C133">
-        <v>200022</v>
-      </c>
-      <c r="D133" t="s">
-        <v>145</v>
-      </c>
-      <c r="H133" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B134" t="s">
-        <v>76</v>
-      </c>
-      <c r="C134">
-        <v>200030</v>
-      </c>
-      <c r="D134" t="s">
-        <v>161</v>
-      </c>
-      <c r="H134" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B135" t="s">
-        <v>76</v>
-      </c>
-      <c r="C135">
-        <v>200031</v>
-      </c>
-      <c r="D135" t="s">
-        <v>162</v>
-      </c>
-      <c r="H135" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B136" t="s">
-        <v>76</v>
-      </c>
-      <c r="C136">
-        <v>200032</v>
-      </c>
-      <c r="D136" t="s">
-        <v>146</v>
-      </c>
-      <c r="H136" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B137" t="s">
-        <v>76</v>
-      </c>
-      <c r="C137">
-        <v>200033</v>
-      </c>
-      <c r="D137" t="s">
-        <v>147</v>
-      </c>
-      <c r="H137" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B138" t="s">
-        <v>76</v>
-      </c>
-      <c r="C138">
-        <v>200034</v>
-      </c>
-      <c r="D138" t="s">
-        <v>148</v>
-      </c>
-      <c r="H138" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B139" t="s">
-        <v>76</v>
-      </c>
-      <c r="C139">
-        <v>200035</v>
-      </c>
-      <c r="D139" t="s">
-        <v>149</v>
-      </c>
-      <c r="H139" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B140" t="s">
-        <v>76</v>
-      </c>
-      <c r="C140">
-        <v>200040</v>
-      </c>
-      <c r="D140" t="s">
-        <v>150</v>
-      </c>
-      <c r="H140" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B141" t="s">
-        <v>76</v>
-      </c>
-      <c r="C141">
-        <v>200050</v>
-      </c>
-      <c r="D141" t="s">
-        <v>151</v>
-      </c>
-      <c r="H141" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B142" t="s">
-        <v>76</v>
-      </c>
-      <c r="C142">
-        <v>200060</v>
-      </c>
-      <c r="D142" t="s">
-        <v>152</v>
-      </c>
-      <c r="H142" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B143" t="s">
-        <v>76</v>
-      </c>
-      <c r="C143">
-        <v>200070</v>
-      </c>
-      <c r="D143" t="s">
-        <v>153</v>
-      </c>
-      <c r="H143" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B144" t="s">
-        <v>76</v>
-      </c>
-      <c r="C144">
-        <v>200080</v>
-      </c>
-      <c r="D144" t="s">
-        <v>154</v>
-      </c>
-      <c r="H144" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B145" t="s">
-        <v>76</v>
-      </c>
-      <c r="C145">
-        <v>200090</v>
-      </c>
-      <c r="D145" t="s">
-        <v>155</v>
-      </c>
-      <c r="H145" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B146" t="s">
-        <v>76</v>
-      </c>
-      <c r="C146">
-        <v>200100</v>
-      </c>
-      <c r="D146" t="s">
-        <v>156</v>
-      </c>
-      <c r="H146" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B147" t="s">
-        <v>76</v>
-      </c>
-      <c r="C147">
-        <v>200101</v>
-      </c>
-      <c r="D147" t="s">
-        <v>157</v>
-      </c>
-      <c r="H147" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B148" t="s">
-        <v>76</v>
-      </c>
-      <c r="C148">
-        <v>200120</v>
-      </c>
-      <c r="D148" t="s">
-        <v>158</v>
-      </c>
-      <c r="H148" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B149" t="s">
-        <v>76</v>
-      </c>
-      <c r="C149">
-        <v>200121</v>
-      </c>
-      <c r="D149" t="s">
-        <v>159</v>
-      </c>
-      <c r="H149" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B150" t="s">
-        <v>76</v>
-      </c>
-      <c r="C150">
-        <v>200122</v>
-      </c>
-      <c r="D150" t="s">
-        <v>160</v>
-      </c>
-      <c r="H150" t="s">
-        <v>67</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>